--- a/outputs/detailed_english.xlsx
+++ b/outputs/detailed_english.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="142">
   <si>
     <t>run_id</t>
   </si>
@@ -163,13 +163,274 @@
     <t>2026-02-27 17:27:35.315843</t>
   </si>
   <si>
+    <t>2026-03-02 16:45:08.677873</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:12.100829</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:15.478613</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:18.789867</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:22.281425</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:26.055071</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:32.702492</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:35.529390</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:39.466445</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:43.977228</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:47.864454</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:52.868060</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:45:58.539992</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:04.214702</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:10.599365</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:13.156549</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:17.611333</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:22.713248</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:26.669114</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:29.798932</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:34.053465</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:37.886240</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:40.869913</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:46.001132</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:46:49.708123</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:47:57.241002</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:01.233108</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:10.454737</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:14.178051</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:18.156738</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:22.960161</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:31.065419</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:36.142016</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:39.023029</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:42.768256</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:45.882110</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:49.555767</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:48:53.596024</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:04.065328</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:13.134323</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:21.335300</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:27.690690</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:30.418414</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:39.255087</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:46.651446</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:51.805303</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:55.307414</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:49:59.038144</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:02.826387</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:06.921358</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:18.319260</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:23.071807</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:31.196851</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:42.130082</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:45.674798</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:51.680937</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:50:58.016059</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:01.314623</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:07.541293</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:11.662457</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:14.667817</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:18.526963</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:27.333213</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:31.454467</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:35.505369</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:39.427618</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:45.382458</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:50.352763</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:51:55.545681</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:52:06.734002</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:52:11.556116</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:52:17.913558</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:52:21.415906</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:52:25.123189</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:52:28.859041</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:53:44.727828</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:53:48.811136</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:53:52.442563</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:53:55.279951</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:02.340112</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:07.046258</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:11.186733</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:15.459959</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:18.122075</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:20.911479</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:24.666033</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:54:28.825376</t>
+  </si>
+  <si>
     <t>ElevenLabs</t>
   </si>
   <si>
     <t>Sarvam</t>
   </si>
   <si>
-    <t>eleven_multilingual_v2</t>
+    <t>eleven_v3</t>
   </si>
   <si>
     <t>bulbul:v3</t>
@@ -202,18 +463,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -245,8 +500,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,11 +797,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O242"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="15" width="15.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
@@ -603,13 +855,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>21</v>
@@ -650,13 +902,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F3">
         <v>21</v>
@@ -697,13 +949,13 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F4">
         <v>84</v>
@@ -744,13 +996,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F5">
         <v>84</v>
@@ -791,13 +1043,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F6">
         <v>33</v>
@@ -838,13 +1090,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F7">
         <v>33</v>
@@ -885,13 +1137,13 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F8">
         <v>40</v>
@@ -932,13 +1184,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -979,13 +1231,13 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F10">
         <v>66</v>
@@ -1026,13 +1278,13 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F11">
         <v>66</v>
@@ -1073,13 +1325,13 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F12">
         <v>47</v>
@@ -1120,13 +1372,13 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F13">
         <v>47</v>
@@ -1167,13 +1419,13 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F14">
         <v>45</v>
@@ -1214,13 +1466,13 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F15">
         <v>45</v>
@@ -1261,13 +1513,13 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F16">
         <v>39</v>
@@ -1308,13 +1560,13 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F17">
         <v>39</v>
@@ -1355,13 +1607,13 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F18">
         <v>50</v>
@@ -1402,13 +1654,13 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F19">
         <v>50</v>
@@ -1449,13 +1701,13 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F20">
         <v>50</v>
@@ -1496,13 +1748,13 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F21">
         <v>91</v>
@@ -1543,13 +1795,13 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F22">
         <v>91</v>
@@ -1590,13 +1842,13 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F23">
         <v>24</v>
@@ -1637,13 +1889,13 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F24">
         <v>24</v>
@@ -1684,13 +1936,13 @@
         <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F25">
         <v>40</v>
@@ -1731,13 +1983,13 @@
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F26">
         <v>40</v>
@@ -1778,13 +2030,13 @@
         <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F27">
         <v>41</v>
@@ -1825,13 +2077,13 @@
         <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F28">
         <v>41</v>
@@ -1872,13 +2124,13 @@
         <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F29">
         <v>37</v>
@@ -1919,13 +2171,13 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F30">
         <v>37</v>
@@ -1966,13 +2218,13 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F31">
         <v>56</v>
@@ -2013,13 +2265,13 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F32">
         <v>56</v>
@@ -2060,13 +2312,13 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F33">
         <v>37</v>
@@ -2107,13 +2359,13 @@
         <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F34">
         <v>37</v>
@@ -2154,13 +2406,13 @@
         <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F35">
         <v>57</v>
@@ -2201,13 +2453,13 @@
         <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F36">
         <v>57</v>
@@ -2248,13 +2500,13 @@
         <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F37">
         <v>55</v>
@@ -2295,13 +2547,13 @@
         <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F38">
         <v>55</v>
@@ -2342,13 +2594,13 @@
         <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F39">
         <v>35</v>
@@ -2389,13 +2641,13 @@
         <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F40">
         <v>35</v>
@@ -2436,13 +2688,13 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F41">
         <v>31</v>
@@ -2483,13 +2735,13 @@
         <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F42">
         <v>31</v>
@@ -2530,13 +2782,13 @@
         <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F43">
         <v>30</v>
@@ -2577,13 +2829,13 @@
         <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F44">
         <v>30</v>
@@ -2624,13 +2876,13 @@
         <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F45">
         <v>30</v>
@@ -2671,13 +2923,13 @@
         <v>37</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F46">
         <v>30</v>
@@ -2718,13 +2970,13 @@
         <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F47">
         <v>44</v>
@@ -2765,13 +3017,13 @@
         <v>38</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E48" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F48">
         <v>44</v>
@@ -2812,13 +3064,13 @@
         <v>39</v>
       </c>
       <c r="C49" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F49">
         <v>46</v>
@@ -2859,13 +3111,13 @@
         <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E50" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F50">
         <v>46</v>
@@ -2906,13 +3158,13 @@
         <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F51">
         <v>46</v>
@@ -2953,13 +3205,13 @@
         <v>40</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E52" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F52">
         <v>46</v>
@@ -3000,13 +3252,13 @@
         <v>41</v>
       </c>
       <c r="C53" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D53" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F53">
         <v>35</v>
@@ -3047,13 +3299,13 @@
         <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F54">
         <v>35</v>
@@ -3094,13 +3346,13 @@
         <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F55">
         <v>33</v>
@@ -3141,13 +3393,13 @@
         <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E56" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F56">
         <v>33</v>
@@ -3188,13 +3440,13 @@
         <v>43</v>
       </c>
       <c r="C57" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F57">
         <v>38</v>
@@ -3235,13 +3487,13 @@
         <v>43</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F58">
         <v>38</v>
@@ -3282,13 +3534,13 @@
         <v>44</v>
       </c>
       <c r="C59" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E59" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F59">
         <v>32</v>
@@ -3329,13 +3581,13 @@
         <v>44</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E60" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F60">
         <v>32</v>
@@ -3376,13 +3628,13 @@
         <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F61">
         <v>92</v>
@@ -3423,13 +3675,13 @@
         <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E62" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F62">
         <v>92</v>
@@ -3470,13 +3722,13 @@
         <v>46</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E63" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F63">
         <v>76</v>
@@ -3517,13 +3769,13 @@
         <v>46</v>
       </c>
       <c r="C64" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E64" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F64">
         <v>76</v>
@@ -3564,13 +3816,13 @@
         <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E65" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F65">
         <v>33</v>
@@ -3611,13 +3863,13 @@
         <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E66" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F66">
         <v>33</v>
@@ -3658,13 +3910,13 @@
         <v>48</v>
       </c>
       <c r="C67" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E67" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F67">
         <v>35</v>
@@ -3705,13 +3957,13 @@
         <v>48</v>
       </c>
       <c r="C68" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E68" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F68">
         <v>35</v>
@@ -3741,6 +3993,8184 @@
         <v>352.94</v>
       </c>
       <c r="O68">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>49</v>
+      </c>
+      <c r="C69" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" t="s">
+        <v>138</v>
+      </c>
+      <c r="E69" t="s">
+        <v>140</v>
+      </c>
+      <c r="F69">
+        <v>41</v>
+      </c>
+      <c r="G69">
+        <v>10</v>
+      </c>
+      <c r="H69">
+        <v>1282.65</v>
+      </c>
+      <c r="I69">
+        <v>2.508</v>
+      </c>
+      <c r="J69">
+        <v>3790.41</v>
+      </c>
+      <c r="K69">
+        <v>10.82</v>
+      </c>
+      <c r="L69">
+        <v>40586</v>
+      </c>
+      <c r="M69">
+        <v>44100</v>
+      </c>
+      <c r="N69">
+        <v>128</v>
+      </c>
+      <c r="O69">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>49</v>
+      </c>
+      <c r="C70" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" t="s">
+        <v>139</v>
+      </c>
+      <c r="E70" t="s">
+        <v>141</v>
+      </c>
+      <c r="F70">
+        <v>41</v>
+      </c>
+      <c r="G70">
+        <v>10</v>
+      </c>
+      <c r="H70">
+        <v>2132.29</v>
+      </c>
+      <c r="I70">
+        <v>4.096</v>
+      </c>
+      <c r="J70">
+        <v>6228.3</v>
+      </c>
+      <c r="K70">
+        <v>6.58</v>
+      </c>
+      <c r="L70">
+        <v>180678</v>
+      </c>
+      <c r="M70">
+        <v>22050</v>
+      </c>
+      <c r="N70">
+        <v>352.89</v>
+      </c>
+      <c r="O70">
+        <v>0.0615</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>50</v>
+      </c>
+      <c r="C71" t="s">
+        <v>136</v>
+      </c>
+      <c r="D71" t="s">
+        <v>138</v>
+      </c>
+      <c r="E71" t="s">
+        <v>140</v>
+      </c>
+      <c r="F71">
+        <v>35</v>
+      </c>
+      <c r="G71">
+        <v>8</v>
+      </c>
+      <c r="H71">
+        <v>1227.27</v>
+      </c>
+      <c r="I71">
+        <v>2.691</v>
+      </c>
+      <c r="J71">
+        <v>3917.89</v>
+      </c>
+      <c r="K71">
+        <v>8.93</v>
+      </c>
+      <c r="L71">
+        <v>43511</v>
+      </c>
+      <c r="M71">
+        <v>44100</v>
+      </c>
+      <c r="N71">
+        <v>128</v>
+      </c>
+      <c r="O71">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>50</v>
+      </c>
+      <c r="C72" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" t="s">
+        <v>139</v>
+      </c>
+      <c r="E72" t="s">
+        <v>141</v>
+      </c>
+      <c r="F72">
+        <v>35</v>
+      </c>
+      <c r="G72">
+        <v>8</v>
+      </c>
+      <c r="H72">
+        <v>2144.53</v>
+      </c>
+      <c r="I72">
+        <v>3.072</v>
+      </c>
+      <c r="J72">
+        <v>5216.55</v>
+      </c>
+      <c r="K72">
+        <v>6.71</v>
+      </c>
+      <c r="L72">
+        <v>135520</v>
+      </c>
+      <c r="M72">
+        <v>22050</v>
+      </c>
+      <c r="N72">
+        <v>352.91</v>
+      </c>
+      <c r="O72">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73" t="s">
+        <v>136</v>
+      </c>
+      <c r="D73" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73" t="s">
+        <v>140</v>
+      </c>
+      <c r="F73">
+        <v>40</v>
+      </c>
+      <c r="G73">
+        <v>9</v>
+      </c>
+      <c r="H73">
+        <v>1274.64</v>
+      </c>
+      <c r="I73">
+        <v>2.821</v>
+      </c>
+      <c r="J73">
+        <v>4095.87</v>
+      </c>
+      <c r="K73">
+        <v>9.77</v>
+      </c>
+      <c r="L73">
+        <v>45601</v>
+      </c>
+      <c r="M73">
+        <v>44100</v>
+      </c>
+      <c r="N73">
+        <v>128</v>
+      </c>
+      <c r="O73">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D74" t="s">
+        <v>139</v>
+      </c>
+      <c r="E74" t="s">
+        <v>141</v>
+      </c>
+      <c r="F74">
+        <v>40</v>
+      </c>
+      <c r="G74">
+        <v>9</v>
+      </c>
+      <c r="H74">
+        <v>2028.6</v>
+      </c>
+      <c r="I74">
+        <v>3.328</v>
+      </c>
+      <c r="J74">
+        <v>5356.58</v>
+      </c>
+      <c r="K74">
+        <v>7.47</v>
+      </c>
+      <c r="L74">
+        <v>146808</v>
+      </c>
+      <c r="M74">
+        <v>22050</v>
+      </c>
+      <c r="N74">
+        <v>352.91</v>
+      </c>
+      <c r="O74">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>52</v>
+      </c>
+      <c r="C75" t="s">
+        <v>136</v>
+      </c>
+      <c r="D75" t="s">
+        <v>138</v>
+      </c>
+      <c r="E75" t="s">
+        <v>140</v>
+      </c>
+      <c r="F75">
+        <v>49</v>
+      </c>
+      <c r="G75">
+        <v>10</v>
+      </c>
+      <c r="H75">
+        <v>1274.92</v>
+      </c>
+      <c r="I75">
+        <v>3.474</v>
+      </c>
+      <c r="J75">
+        <v>4749.21</v>
+      </c>
+      <c r="K75">
+        <v>10.32</v>
+      </c>
+      <c r="L75">
+        <v>56050</v>
+      </c>
+      <c r="M75">
+        <v>44100</v>
+      </c>
+      <c r="N75">
+        <v>128</v>
+      </c>
+      <c r="O75">
+        <v>0.196</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76" t="s">
+        <v>137</v>
+      </c>
+      <c r="D76" t="s">
+        <v>139</v>
+      </c>
+      <c r="E76" t="s">
+        <v>141</v>
+      </c>
+      <c r="F76">
+        <v>49</v>
+      </c>
+      <c r="G76">
+        <v>10</v>
+      </c>
+      <c r="H76">
+        <v>2209.27</v>
+      </c>
+      <c r="I76">
+        <v>4.352</v>
+      </c>
+      <c r="J76">
+        <v>6561.29</v>
+      </c>
+      <c r="K76">
+        <v>7.47</v>
+      </c>
+      <c r="L76">
+        <v>191968</v>
+      </c>
+      <c r="M76">
+        <v>22050</v>
+      </c>
+      <c r="N76">
+        <v>352.88</v>
+      </c>
+      <c r="O76">
+        <v>0.0735</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" t="s">
+        <v>136</v>
+      </c>
+      <c r="D77" t="s">
+        <v>138</v>
+      </c>
+      <c r="E77" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77">
+        <v>63</v>
+      </c>
+      <c r="G77">
+        <v>14</v>
+      </c>
+      <c r="H77">
+        <v>1372.14</v>
+      </c>
+      <c r="I77">
+        <v>4.598</v>
+      </c>
+      <c r="J77">
+        <v>5969.69</v>
+      </c>
+      <c r="K77">
+        <v>10.55</v>
+      </c>
+      <c r="L77">
+        <v>74022</v>
+      </c>
+      <c r="M77">
+        <v>44100</v>
+      </c>
+      <c r="N77">
+        <v>128</v>
+      </c>
+      <c r="O77">
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D78" t="s">
+        <v>139</v>
+      </c>
+      <c r="E78" t="s">
+        <v>141</v>
+      </c>
+      <c r="F78">
+        <v>63</v>
+      </c>
+      <c r="G78">
+        <v>14</v>
+      </c>
+      <c r="H78">
+        <v>2394.57</v>
+      </c>
+      <c r="I78">
+        <v>4.949</v>
+      </c>
+      <c r="J78">
+        <v>7343.91</v>
+      </c>
+      <c r="K78">
+        <v>8.58</v>
+      </c>
+      <c r="L78">
+        <v>218310</v>
+      </c>
+      <c r="M78">
+        <v>22050</v>
+      </c>
+      <c r="N78">
+        <v>352.87</v>
+      </c>
+      <c r="O78">
+        <v>0.0945</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" t="s">
+        <v>138</v>
+      </c>
+      <c r="E79" t="s">
+        <v>140</v>
+      </c>
+      <c r="F79">
+        <v>39</v>
+      </c>
+      <c r="G79">
+        <v>9</v>
+      </c>
+      <c r="H79">
+        <v>1318.93</v>
+      </c>
+      <c r="I79">
+        <v>2.873</v>
+      </c>
+      <c r="J79">
+        <v>4192.4</v>
+      </c>
+      <c r="K79">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L79">
+        <v>46437</v>
+      </c>
+      <c r="M79">
+        <v>44100</v>
+      </c>
+      <c r="N79">
+        <v>128</v>
+      </c>
+      <c r="O79">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" t="s">
+        <v>137</v>
+      </c>
+      <c r="D80" t="s">
+        <v>139</v>
+      </c>
+      <c r="E80" t="s">
+        <v>141</v>
+      </c>
+      <c r="F80">
+        <v>39</v>
+      </c>
+      <c r="G80">
+        <v>9</v>
+      </c>
+      <c r="H80">
+        <v>5320.63</v>
+      </c>
+      <c r="I80">
+        <v>3.072</v>
+      </c>
+      <c r="J80">
+        <v>8392.65</v>
+      </c>
+      <c r="K80">
+        <v>4.65</v>
+      </c>
+      <c r="L80">
+        <v>135520</v>
+      </c>
+      <c r="M80">
+        <v>22050</v>
+      </c>
+      <c r="N80">
+        <v>352.91</v>
+      </c>
+      <c r="O80">
+        <v>0.0585</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" t="s">
+        <v>136</v>
+      </c>
+      <c r="D81" t="s">
+        <v>138</v>
+      </c>
+      <c r="E81" t="s">
+        <v>140</v>
+      </c>
+      <c r="F81">
+        <v>33</v>
+      </c>
+      <c r="G81">
+        <v>7</v>
+      </c>
+      <c r="H81">
+        <v>1358.9</v>
+      </c>
+      <c r="I81">
+        <v>2.22</v>
+      </c>
+      <c r="J81">
+        <v>3579.31</v>
+      </c>
+      <c r="K81">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L81">
+        <v>35988</v>
+      </c>
+      <c r="M81">
+        <v>44100</v>
+      </c>
+      <c r="N81">
+        <v>128</v>
+      </c>
+      <c r="O81">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>55</v>
+      </c>
+      <c r="C82" t="s">
+        <v>137</v>
+      </c>
+      <c r="D82" t="s">
+        <v>139</v>
+      </c>
+      <c r="E82" t="s">
+        <v>141</v>
+      </c>
+      <c r="F82">
+        <v>33</v>
+      </c>
+      <c r="G82">
+        <v>7</v>
+      </c>
+      <c r="H82">
+        <v>1460.91</v>
+      </c>
+      <c r="I82">
+        <v>2.048</v>
+      </c>
+      <c r="J82">
+        <v>3508.89</v>
+      </c>
+      <c r="K82">
+        <v>9.4</v>
+      </c>
+      <c r="L82">
+        <v>90360</v>
+      </c>
+      <c r="M82">
+        <v>22050</v>
+      </c>
+      <c r="N82">
+        <v>352.97</v>
+      </c>
+      <c r="O82">
+        <v>0.0495</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" t="s">
+        <v>136</v>
+      </c>
+      <c r="D83" t="s">
+        <v>138</v>
+      </c>
+      <c r="E83" t="s">
+        <v>140</v>
+      </c>
+      <c r="F83">
+        <v>62</v>
+      </c>
+      <c r="G83">
+        <v>13</v>
+      </c>
+      <c r="H83">
+        <v>1331.03</v>
+      </c>
+      <c r="I83">
+        <v>4.441</v>
+      </c>
+      <c r="J83">
+        <v>5771.85</v>
+      </c>
+      <c r="K83">
+        <v>10.74</v>
+      </c>
+      <c r="L83">
+        <v>71515</v>
+      </c>
+      <c r="M83">
+        <v>44100</v>
+      </c>
+      <c r="N83">
+        <v>128</v>
+      </c>
+      <c r="O83">
+        <v>0.248</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" t="s">
+        <v>137</v>
+      </c>
+      <c r="D84" t="s">
+        <v>139</v>
+      </c>
+      <c r="E84" t="s">
+        <v>141</v>
+      </c>
+      <c r="F84">
+        <v>62</v>
+      </c>
+      <c r="G84">
+        <v>13</v>
+      </c>
+      <c r="H84">
+        <v>2596.03</v>
+      </c>
+      <c r="I84">
+        <v>5.376</v>
+      </c>
+      <c r="J84">
+        <v>7972.04</v>
+      </c>
+      <c r="K84">
+        <v>7.78</v>
+      </c>
+      <c r="L84">
+        <v>237126</v>
+      </c>
+      <c r="M84">
+        <v>22050</v>
+      </c>
+      <c r="N84">
+        <v>352.87</v>
+      </c>
+      <c r="O84">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>57</v>
+      </c>
+      <c r="C85" t="s">
+        <v>136</v>
+      </c>
+      <c r="D85" t="s">
+        <v>138</v>
+      </c>
+      <c r="E85" t="s">
+        <v>140</v>
+      </c>
+      <c r="F85">
+        <v>35</v>
+      </c>
+      <c r="G85">
+        <v>8</v>
+      </c>
+      <c r="H85">
+        <v>1383.03</v>
+      </c>
+      <c r="I85">
+        <v>2.508</v>
+      </c>
+      <c r="J85">
+        <v>3890.79</v>
+      </c>
+      <c r="K85">
+        <v>9</v>
+      </c>
+      <c r="L85">
+        <v>40586</v>
+      </c>
+      <c r="M85">
+        <v>44100</v>
+      </c>
+      <c r="N85">
+        <v>128</v>
+      </c>
+      <c r="O85">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86" t="s">
+        <v>137</v>
+      </c>
+      <c r="D86" t="s">
+        <v>139</v>
+      </c>
+      <c r="E86" t="s">
+        <v>141</v>
+      </c>
+      <c r="F86">
+        <v>35</v>
+      </c>
+      <c r="G86">
+        <v>8</v>
+      </c>
+      <c r="H86">
+        <v>3121.71</v>
+      </c>
+      <c r="I86">
+        <v>3.243</v>
+      </c>
+      <c r="J86">
+        <v>6364.38</v>
+      </c>
+      <c r="K86">
+        <v>5.5</v>
+      </c>
+      <c r="L86">
+        <v>143046</v>
+      </c>
+      <c r="M86">
+        <v>22050</v>
+      </c>
+      <c r="N86">
+        <v>352.91</v>
+      </c>
+      <c r="O86">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" t="s">
+        <v>136</v>
+      </c>
+      <c r="D87" t="s">
+        <v>138</v>
+      </c>
+      <c r="E87" t="s">
+        <v>140</v>
+      </c>
+      <c r="F87">
+        <v>34</v>
+      </c>
+      <c r="G87">
+        <v>8</v>
+      </c>
+      <c r="H87">
+        <v>1417.64</v>
+      </c>
+      <c r="I87">
+        <v>2.534</v>
+      </c>
+      <c r="J87">
+        <v>3951.51</v>
+      </c>
+      <c r="K87">
+        <v>8.6</v>
+      </c>
+      <c r="L87">
+        <v>41004</v>
+      </c>
+      <c r="M87">
+        <v>44100</v>
+      </c>
+      <c r="N87">
+        <v>128</v>
+      </c>
+      <c r="O87">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" t="s">
+        <v>137</v>
+      </c>
+      <c r="D88" t="s">
+        <v>139</v>
+      </c>
+      <c r="E88" t="s">
+        <v>141</v>
+      </c>
+      <c r="F88">
+        <v>34</v>
+      </c>
+      <c r="G88">
+        <v>8</v>
+      </c>
+      <c r="H88">
+        <v>2462.69</v>
+      </c>
+      <c r="I88">
+        <v>3.328</v>
+      </c>
+      <c r="J88">
+        <v>5790.67</v>
+      </c>
+      <c r="K88">
+        <v>5.87</v>
+      </c>
+      <c r="L88">
+        <v>146808</v>
+      </c>
+      <c r="M88">
+        <v>22050</v>
+      </c>
+      <c r="N88">
+        <v>352.91</v>
+      </c>
+      <c r="O88">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>59</v>
+      </c>
+      <c r="C89" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" t="s">
+        <v>138</v>
+      </c>
+      <c r="E89" t="s">
+        <v>140</v>
+      </c>
+      <c r="F89">
+        <v>46</v>
+      </c>
+      <c r="G89">
+        <v>9</v>
+      </c>
+      <c r="H89">
+        <v>1652.99</v>
+      </c>
+      <c r="I89">
+        <v>3.37</v>
+      </c>
+      <c r="J89">
+        <v>5022.78</v>
+      </c>
+      <c r="K89">
+        <v>9.16</v>
+      </c>
+      <c r="L89">
+        <v>54378</v>
+      </c>
+      <c r="M89">
+        <v>44100</v>
+      </c>
+      <c r="N89">
+        <v>128</v>
+      </c>
+      <c r="O89">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>59</v>
+      </c>
+      <c r="C90" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" t="s">
+        <v>139</v>
+      </c>
+      <c r="E90" t="s">
+        <v>141</v>
+      </c>
+      <c r="F90">
+        <v>46</v>
+      </c>
+      <c r="G90">
+        <v>9</v>
+      </c>
+      <c r="H90">
+        <v>3338.66</v>
+      </c>
+      <c r="I90">
+        <v>4.523</v>
+      </c>
+      <c r="J90">
+        <v>7861.34</v>
+      </c>
+      <c r="K90">
+        <v>5.85</v>
+      </c>
+      <c r="L90">
+        <v>199494</v>
+      </c>
+      <c r="M90">
+        <v>22050</v>
+      </c>
+      <c r="N90">
+        <v>352.88</v>
+      </c>
+      <c r="O90">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>60</v>
+      </c>
+      <c r="C91" t="s">
+        <v>136</v>
+      </c>
+      <c r="D91" t="s">
+        <v>138</v>
+      </c>
+      <c r="E91" t="s">
+        <v>140</v>
+      </c>
+      <c r="F91">
+        <v>58</v>
+      </c>
+      <c r="G91">
+        <v>13</v>
+      </c>
+      <c r="H91">
+        <v>2836.42</v>
+      </c>
+      <c r="I91">
+        <v>3.84</v>
+      </c>
+      <c r="J91">
+        <v>6676.42</v>
+      </c>
+      <c r="K91">
+        <v>8.69</v>
+      </c>
+      <c r="L91">
+        <v>61902</v>
+      </c>
+      <c r="M91">
+        <v>44100</v>
+      </c>
+      <c r="N91">
+        <v>128</v>
+      </c>
+      <c r="O91">
+        <v>0.232</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>60</v>
+      </c>
+      <c r="C92" t="s">
+        <v>137</v>
+      </c>
+      <c r="D92" t="s">
+        <v>139</v>
+      </c>
+      <c r="E92" t="s">
+        <v>141</v>
+      </c>
+      <c r="F92">
+        <v>58</v>
+      </c>
+      <c r="G92">
+        <v>13</v>
+      </c>
+      <c r="H92">
+        <v>2828.49</v>
+      </c>
+      <c r="I92">
+        <v>4.949</v>
+      </c>
+      <c r="J92">
+        <v>7777.83</v>
+      </c>
+      <c r="K92">
+        <v>7.46</v>
+      </c>
+      <c r="L92">
+        <v>218310</v>
+      </c>
+      <c r="M92">
+        <v>22050</v>
+      </c>
+      <c r="N92">
+        <v>352.87</v>
+      </c>
+      <c r="O92">
+        <v>0.08699999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>61</v>
+      </c>
+      <c r="C93" t="s">
+        <v>136</v>
+      </c>
+      <c r="D93" t="s">
+        <v>138</v>
+      </c>
+      <c r="E93" t="s">
+        <v>140</v>
+      </c>
+      <c r="F93">
+        <v>47</v>
+      </c>
+      <c r="G93">
+        <v>10</v>
+      </c>
+      <c r="H93">
+        <v>3301.22</v>
+      </c>
+      <c r="I93">
+        <v>4.127</v>
+      </c>
+      <c r="J93">
+        <v>7428.56</v>
+      </c>
+      <c r="K93">
+        <v>6.33</v>
+      </c>
+      <c r="L93">
+        <v>66499</v>
+      </c>
+      <c r="M93">
+        <v>44100</v>
+      </c>
+      <c r="N93">
+        <v>128</v>
+      </c>
+      <c r="O93">
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>61</v>
+      </c>
+      <c r="C94" t="s">
+        <v>137</v>
+      </c>
+      <c r="D94" t="s">
+        <v>139</v>
+      </c>
+      <c r="E94" t="s">
+        <v>141</v>
+      </c>
+      <c r="F94">
+        <v>47</v>
+      </c>
+      <c r="G94">
+        <v>10</v>
+      </c>
+      <c r="H94">
+        <v>2365.57</v>
+      </c>
+      <c r="I94">
+        <v>4.352</v>
+      </c>
+      <c r="J94">
+        <v>6717.59</v>
+      </c>
+      <c r="K94">
+        <v>7</v>
+      </c>
+      <c r="L94">
+        <v>191968</v>
+      </c>
+      <c r="M94">
+        <v>22050</v>
+      </c>
+      <c r="N94">
+        <v>352.88</v>
+      </c>
+      <c r="O94">
+        <v>0.07049999999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" t="s">
+        <v>136</v>
+      </c>
+      <c r="D95" t="s">
+        <v>138</v>
+      </c>
+      <c r="E95" t="s">
+        <v>140</v>
+      </c>
+      <c r="F95">
+        <v>71</v>
+      </c>
+      <c r="G95">
+        <v>15</v>
+      </c>
+      <c r="H95">
+        <v>1970.19</v>
+      </c>
+      <c r="I95">
+        <v>5.251</v>
+      </c>
+      <c r="J95">
+        <v>7220.8</v>
+      </c>
+      <c r="K95">
+        <v>9.83</v>
+      </c>
+      <c r="L95">
+        <v>84471</v>
+      </c>
+      <c r="M95">
+        <v>44100</v>
+      </c>
+      <c r="N95">
+        <v>128</v>
+      </c>
+      <c r="O95">
+        <v>0.284</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>62</v>
+      </c>
+      <c r="C96" t="s">
+        <v>137</v>
+      </c>
+      <c r="D96" t="s">
+        <v>139</v>
+      </c>
+      <c r="E96" t="s">
+        <v>141</v>
+      </c>
+      <c r="F96">
+        <v>71</v>
+      </c>
+      <c r="G96">
+        <v>15</v>
+      </c>
+      <c r="H96">
+        <v>4405.08</v>
+      </c>
+      <c r="I96">
+        <v>5.803</v>
+      </c>
+      <c r="J96">
+        <v>10207.76</v>
+      </c>
+      <c r="K96">
+        <v>6.96</v>
+      </c>
+      <c r="L96">
+        <v>255942</v>
+      </c>
+      <c r="M96">
+        <v>22050</v>
+      </c>
+      <c r="N96">
+        <v>352.86</v>
+      </c>
+      <c r="O96">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>63</v>
+      </c>
+      <c r="C97" t="s">
+        <v>136</v>
+      </c>
+      <c r="D97" t="s">
+        <v>138</v>
+      </c>
+      <c r="E97" t="s">
+        <v>140</v>
+      </c>
+      <c r="F97">
+        <v>21</v>
+      </c>
+      <c r="G97">
+        <v>5</v>
+      </c>
+      <c r="H97">
+        <v>1190.88</v>
+      </c>
+      <c r="I97">
+        <v>1.933</v>
+      </c>
+      <c r="J97">
+        <v>3123.94</v>
+      </c>
+      <c r="K97">
+        <v>6.72</v>
+      </c>
+      <c r="L97">
+        <v>31391</v>
+      </c>
+      <c r="M97">
+        <v>44100</v>
+      </c>
+      <c r="N97">
+        <v>128</v>
+      </c>
+      <c r="O97">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>63</v>
+      </c>
+      <c r="C98" t="s">
+        <v>137</v>
+      </c>
+      <c r="D98" t="s">
+        <v>139</v>
+      </c>
+      <c r="E98" t="s">
+        <v>141</v>
+      </c>
+      <c r="F98">
+        <v>21</v>
+      </c>
+      <c r="G98">
+        <v>5</v>
+      </c>
+      <c r="H98">
+        <v>1352.28</v>
+      </c>
+      <c r="I98">
+        <v>1.963</v>
+      </c>
+      <c r="J98">
+        <v>3314.96</v>
+      </c>
+      <c r="K98">
+        <v>6.33</v>
+      </c>
+      <c r="L98">
+        <v>86598</v>
+      </c>
+      <c r="M98">
+        <v>22050</v>
+      </c>
+      <c r="N98">
+        <v>352.98</v>
+      </c>
+      <c r="O98">
+        <v>0.0315</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" t="s">
+        <v>136</v>
+      </c>
+      <c r="D99" t="s">
+        <v>138</v>
+      </c>
+      <c r="E99" t="s">
+        <v>140</v>
+      </c>
+      <c r="F99">
+        <v>61</v>
+      </c>
+      <c r="G99">
+        <v>13</v>
+      </c>
+      <c r="H99">
+        <v>1414.15</v>
+      </c>
+      <c r="I99">
+        <v>4.441</v>
+      </c>
+      <c r="J99">
+        <v>5854.97</v>
+      </c>
+      <c r="K99">
+        <v>10.42</v>
+      </c>
+      <c r="L99">
+        <v>71515</v>
+      </c>
+      <c r="M99">
+        <v>44100</v>
+      </c>
+      <c r="N99">
+        <v>128</v>
+      </c>
+      <c r="O99">
+        <v>0.244</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>64</v>
+      </c>
+      <c r="C100" t="s">
+        <v>137</v>
+      </c>
+      <c r="D100" t="s">
+        <v>139</v>
+      </c>
+      <c r="E100" t="s">
+        <v>141</v>
+      </c>
+      <c r="F100">
+        <v>61</v>
+      </c>
+      <c r="G100">
+        <v>13</v>
+      </c>
+      <c r="H100">
+        <v>3023.54</v>
+      </c>
+      <c r="I100">
+        <v>5.035</v>
+      </c>
+      <c r="J100">
+        <v>8058.19</v>
+      </c>
+      <c r="K100">
+        <v>7.57</v>
+      </c>
+      <c r="L100">
+        <v>222072</v>
+      </c>
+      <c r="M100">
+        <v>22050</v>
+      </c>
+      <c r="N100">
+        <v>352.87</v>
+      </c>
+      <c r="O100">
+        <v>0.0915</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C101" t="s">
+        <v>136</v>
+      </c>
+      <c r="D101" t="s">
+        <v>138</v>
+      </c>
+      <c r="E101" t="s">
+        <v>140</v>
+      </c>
+      <c r="F101">
+        <v>34</v>
+      </c>
+      <c r="G101">
+        <v>7</v>
+      </c>
+      <c r="H101">
+        <v>1506.95</v>
+      </c>
+      <c r="I101">
+        <v>2.22</v>
+      </c>
+      <c r="J101">
+        <v>3727.36</v>
+      </c>
+      <c r="K101">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="L101">
+        <v>35988</v>
+      </c>
+      <c r="M101">
+        <v>44100</v>
+      </c>
+      <c r="N101">
+        <v>128</v>
+      </c>
+      <c r="O101">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" t="s">
+        <v>137</v>
+      </c>
+      <c r="D102" t="s">
+        <v>139</v>
+      </c>
+      <c r="E102" t="s">
+        <v>141</v>
+      </c>
+      <c r="F102">
+        <v>34</v>
+      </c>
+      <c r="G102">
+        <v>7</v>
+      </c>
+      <c r="H102">
+        <v>3575.88</v>
+      </c>
+      <c r="I102">
+        <v>2.645</v>
+      </c>
+      <c r="J102">
+        <v>6221.23</v>
+      </c>
+      <c r="K102">
+        <v>5.47</v>
+      </c>
+      <c r="L102">
+        <v>116704</v>
+      </c>
+      <c r="M102">
+        <v>22050</v>
+      </c>
+      <c r="N102">
+        <v>352.93</v>
+      </c>
+      <c r="O102">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>66</v>
+      </c>
+      <c r="C103" t="s">
+        <v>136</v>
+      </c>
+      <c r="D103" t="s">
+        <v>138</v>
+      </c>
+      <c r="E103" t="s">
+        <v>140</v>
+      </c>
+      <c r="F103">
+        <v>62</v>
+      </c>
+      <c r="G103">
+        <v>15</v>
+      </c>
+      <c r="H103">
+        <v>1435.34</v>
+      </c>
+      <c r="I103">
+        <v>4.833</v>
+      </c>
+      <c r="J103">
+        <v>6267.99</v>
+      </c>
+      <c r="K103">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="L103">
+        <v>77784</v>
+      </c>
+      <c r="M103">
+        <v>44100</v>
+      </c>
+      <c r="N103">
+        <v>128</v>
+      </c>
+      <c r="O103">
+        <v>0.248</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>66</v>
+      </c>
+      <c r="C104" t="s">
+        <v>137</v>
+      </c>
+      <c r="D104" t="s">
+        <v>139</v>
+      </c>
+      <c r="E104" t="s">
+        <v>141</v>
+      </c>
+      <c r="F104">
+        <v>62</v>
+      </c>
+      <c r="G104">
+        <v>15</v>
+      </c>
+      <c r="H104">
+        <v>2503.48</v>
+      </c>
+      <c r="I104">
+        <v>4.011</v>
+      </c>
+      <c r="J104">
+        <v>6514.14</v>
+      </c>
+      <c r="K104">
+        <v>9.52</v>
+      </c>
+      <c r="L104">
+        <v>176914</v>
+      </c>
+      <c r="M104">
+        <v>22050</v>
+      </c>
+      <c r="N104">
+        <v>352.89</v>
+      </c>
+      <c r="O104">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>67</v>
+      </c>
+      <c r="C105" t="s">
+        <v>136</v>
+      </c>
+      <c r="D105" t="s">
+        <v>138</v>
+      </c>
+      <c r="E105" t="s">
+        <v>140</v>
+      </c>
+      <c r="F105">
+        <v>31</v>
+      </c>
+      <c r="G105">
+        <v>8</v>
+      </c>
+      <c r="H105">
+        <v>1311.27</v>
+      </c>
+      <c r="I105">
+        <v>2.743</v>
+      </c>
+      <c r="J105">
+        <v>4054.13</v>
+      </c>
+      <c r="K105">
+        <v>7.65</v>
+      </c>
+      <c r="L105">
+        <v>44347</v>
+      </c>
+      <c r="M105">
+        <v>44100</v>
+      </c>
+      <c r="N105">
+        <v>128</v>
+      </c>
+      <c r="O105">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>67</v>
+      </c>
+      <c r="C106" t="s">
+        <v>137</v>
+      </c>
+      <c r="D106" t="s">
+        <v>139</v>
+      </c>
+      <c r="E106" t="s">
+        <v>141</v>
+      </c>
+      <c r="F106">
+        <v>31</v>
+      </c>
+      <c r="G106">
+        <v>8</v>
+      </c>
+      <c r="H106">
+        <v>1804.52</v>
+      </c>
+      <c r="I106">
+        <v>2.816</v>
+      </c>
+      <c r="J106">
+        <v>4620.53</v>
+      </c>
+      <c r="K106">
+        <v>6.71</v>
+      </c>
+      <c r="L106">
+        <v>124230</v>
+      </c>
+      <c r="M106">
+        <v>22050</v>
+      </c>
+      <c r="N106">
+        <v>352.92</v>
+      </c>
+      <c r="O106">
+        <v>0.0465</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>68</v>
+      </c>
+      <c r="C107" t="s">
+        <v>136</v>
+      </c>
+      <c r="D107" t="s">
+        <v>138</v>
+      </c>
+      <c r="E107" t="s">
+        <v>140</v>
+      </c>
+      <c r="F107">
+        <v>67</v>
+      </c>
+      <c r="G107">
+        <v>14</v>
+      </c>
+      <c r="H107">
+        <v>1383.23</v>
+      </c>
+      <c r="I107">
+        <v>4.728</v>
+      </c>
+      <c r="J107">
+        <v>6111.39</v>
+      </c>
+      <c r="K107">
+        <v>10.96</v>
+      </c>
+      <c r="L107">
+        <v>76112</v>
+      </c>
+      <c r="M107">
+        <v>44100</v>
+      </c>
+      <c r="N107">
+        <v>128</v>
+      </c>
+      <c r="O107">
+        <v>0.268</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>68</v>
+      </c>
+      <c r="C108" t="s">
+        <v>137</v>
+      </c>
+      <c r="D108" t="s">
+        <v>139</v>
+      </c>
+      <c r="E108" t="s">
+        <v>141</v>
+      </c>
+      <c r="F108">
+        <v>67</v>
+      </c>
+      <c r="G108">
+        <v>14</v>
+      </c>
+      <c r="H108">
+        <v>2853.25</v>
+      </c>
+      <c r="I108">
+        <v>4.523</v>
+      </c>
+      <c r="J108">
+        <v>7375.93</v>
+      </c>
+      <c r="K108">
+        <v>9.08</v>
+      </c>
+      <c r="L108">
+        <v>199494</v>
+      </c>
+      <c r="M108">
+        <v>22050</v>
+      </c>
+      <c r="N108">
+        <v>352.88</v>
+      </c>
+      <c r="O108">
+        <v>0.1005</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>69</v>
+      </c>
+      <c r="C109" t="s">
+        <v>136</v>
+      </c>
+      <c r="D109" t="s">
+        <v>138</v>
+      </c>
+      <c r="E109" t="s">
+        <v>140</v>
+      </c>
+      <c r="F109">
+        <v>55</v>
+      </c>
+      <c r="G109">
+        <v>12</v>
+      </c>
+      <c r="H109">
+        <v>1313.65</v>
+      </c>
+      <c r="I109">
+        <v>4.206</v>
+      </c>
+      <c r="J109">
+        <v>5519.37</v>
+      </c>
+      <c r="K109">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="L109">
+        <v>67753</v>
+      </c>
+      <c r="M109">
+        <v>44100</v>
+      </c>
+      <c r="N109">
+        <v>128</v>
+      </c>
+      <c r="O109">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>69</v>
+      </c>
+      <c r="C110" t="s">
+        <v>137</v>
+      </c>
+      <c r="D110" t="s">
+        <v>139</v>
+      </c>
+      <c r="E110" t="s">
+        <v>141</v>
+      </c>
+      <c r="F110">
+        <v>55</v>
+      </c>
+      <c r="G110">
+        <v>12</v>
+      </c>
+      <c r="H110">
+        <v>2500.97</v>
+      </c>
+      <c r="I110">
+        <v>4.779</v>
+      </c>
+      <c r="J110">
+        <v>7279.65</v>
+      </c>
+      <c r="K110">
+        <v>7.56</v>
+      </c>
+      <c r="L110">
+        <v>210784</v>
+      </c>
+      <c r="M110">
+        <v>22050</v>
+      </c>
+      <c r="N110">
+        <v>352.87</v>
+      </c>
+      <c r="O110">
+        <v>0.0825</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>70</v>
+      </c>
+      <c r="C111" t="s">
+        <v>136</v>
+      </c>
+      <c r="D111" t="s">
+        <v>138</v>
+      </c>
+      <c r="E111" t="s">
+        <v>140</v>
+      </c>
+      <c r="F111">
+        <v>40</v>
+      </c>
+      <c r="G111">
+        <v>9</v>
+      </c>
+      <c r="H111">
+        <v>1203.89</v>
+      </c>
+      <c r="I111">
+        <v>2.769</v>
+      </c>
+      <c r="J111">
+        <v>3972.87</v>
+      </c>
+      <c r="K111">
+        <v>10.07</v>
+      </c>
+      <c r="L111">
+        <v>44765</v>
+      </c>
+      <c r="M111">
+        <v>44100</v>
+      </c>
+      <c r="N111">
+        <v>128</v>
+      </c>
+      <c r="O111">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>70</v>
+      </c>
+      <c r="C112" t="s">
+        <v>137</v>
+      </c>
+      <c r="D112" t="s">
+        <v>139</v>
+      </c>
+      <c r="E112" t="s">
+        <v>141</v>
+      </c>
+      <c r="F112">
+        <v>40</v>
+      </c>
+      <c r="G112">
+        <v>9</v>
+      </c>
+      <c r="H112">
+        <v>1763.62</v>
+      </c>
+      <c r="I112">
+        <v>2.987</v>
+      </c>
+      <c r="J112">
+        <v>4750.29</v>
+      </c>
+      <c r="K112">
+        <v>8.42</v>
+      </c>
+      <c r="L112">
+        <v>131756</v>
+      </c>
+      <c r="M112">
+        <v>22050</v>
+      </c>
+      <c r="N112">
+        <v>352.92</v>
+      </c>
+      <c r="O112">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>71</v>
+      </c>
+      <c r="C113" t="s">
+        <v>136</v>
+      </c>
+      <c r="D113" t="s">
+        <v>138</v>
+      </c>
+      <c r="E113" t="s">
+        <v>140</v>
+      </c>
+      <c r="F113">
+        <v>86</v>
+      </c>
+      <c r="G113">
+        <v>19</v>
+      </c>
+      <c r="H113">
+        <v>1573.45</v>
+      </c>
+      <c r="I113">
+        <v>6.4</v>
+      </c>
+      <c r="J113">
+        <v>7973.45</v>
+      </c>
+      <c r="K113">
+        <v>10.79</v>
+      </c>
+      <c r="L113">
+        <v>102862</v>
+      </c>
+      <c r="M113">
+        <v>44100</v>
+      </c>
+      <c r="N113">
+        <v>128</v>
+      </c>
+      <c r="O113">
+        <v>0.344</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>71</v>
+      </c>
+      <c r="C114" t="s">
+        <v>137</v>
+      </c>
+      <c r="D114" t="s">
+        <v>139</v>
+      </c>
+      <c r="E114" t="s">
+        <v>141</v>
+      </c>
+      <c r="F114">
+        <v>86</v>
+      </c>
+      <c r="G114">
+        <v>19</v>
+      </c>
+      <c r="H114">
+        <v>3538.96</v>
+      </c>
+      <c r="I114">
+        <v>7.253</v>
+      </c>
+      <c r="J114">
+        <v>10792.29</v>
+      </c>
+      <c r="K114">
+        <v>7.97</v>
+      </c>
+      <c r="L114">
+        <v>319916</v>
+      </c>
+      <c r="M114">
+        <v>22050</v>
+      </c>
+      <c r="N114">
+        <v>352.85</v>
+      </c>
+      <c r="O114">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>72</v>
+      </c>
+      <c r="C115" t="s">
+        <v>136</v>
+      </c>
+      <c r="D115" t="s">
+        <v>138</v>
+      </c>
+      <c r="E115" t="s">
+        <v>140</v>
+      </c>
+      <c r="F115">
+        <v>42</v>
+      </c>
+      <c r="G115">
+        <v>9</v>
+      </c>
+      <c r="H115">
+        <v>1339.88</v>
+      </c>
+      <c r="I115">
+        <v>3.291</v>
+      </c>
+      <c r="J115">
+        <v>4631.31</v>
+      </c>
+      <c r="K115">
+        <v>9.07</v>
+      </c>
+      <c r="L115">
+        <v>53124</v>
+      </c>
+      <c r="M115">
+        <v>44100</v>
+      </c>
+      <c r="N115">
+        <v>128</v>
+      </c>
+      <c r="O115">
+        <v>0.168</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>72</v>
+      </c>
+      <c r="C116" t="s">
+        <v>137</v>
+      </c>
+      <c r="D116" t="s">
+        <v>139</v>
+      </c>
+      <c r="E116" t="s">
+        <v>141</v>
+      </c>
+      <c r="F116">
+        <v>42</v>
+      </c>
+      <c r="G116">
+        <v>9</v>
+      </c>
+      <c r="H116">
+        <v>2348.52</v>
+      </c>
+      <c r="I116">
+        <v>3.499</v>
+      </c>
+      <c r="J116">
+        <v>5847.21</v>
+      </c>
+      <c r="K116">
+        <v>7.18</v>
+      </c>
+      <c r="L116">
+        <v>154336</v>
+      </c>
+      <c r="M116">
+        <v>22050</v>
+      </c>
+      <c r="N116">
+        <v>352.9</v>
+      </c>
+      <c r="O116">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>73</v>
+      </c>
+      <c r="C117" t="s">
+        <v>136</v>
+      </c>
+      <c r="D117" t="s">
+        <v>138</v>
+      </c>
+      <c r="E117" t="s">
+        <v>140</v>
+      </c>
+      <c r="F117">
+        <v>42</v>
+      </c>
+      <c r="G117">
+        <v>10</v>
+      </c>
+      <c r="H117">
+        <v>1311.77</v>
+      </c>
+      <c r="I117">
+        <v>2.873</v>
+      </c>
+      <c r="J117">
+        <v>4185.24</v>
+      </c>
+      <c r="K117">
+        <v>10.04</v>
+      </c>
+      <c r="L117">
+        <v>46437</v>
+      </c>
+      <c r="M117">
+        <v>44100</v>
+      </c>
+      <c r="N117">
+        <v>128</v>
+      </c>
+      <c r="O117">
+        <v>0.168</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" t="s">
+        <v>137</v>
+      </c>
+      <c r="D118" t="s">
+        <v>139</v>
+      </c>
+      <c r="E118" t="s">
+        <v>141</v>
+      </c>
+      <c r="F118">
+        <v>42</v>
+      </c>
+      <c r="G118">
+        <v>10</v>
+      </c>
+      <c r="H118">
+        <v>2430.9</v>
+      </c>
+      <c r="I118">
+        <v>4.011</v>
+      </c>
+      <c r="J118">
+        <v>6441.56</v>
+      </c>
+      <c r="K118">
+        <v>6.52</v>
+      </c>
+      <c r="L118">
+        <v>176914</v>
+      </c>
+      <c r="M118">
+        <v>22050</v>
+      </c>
+      <c r="N118">
+        <v>352.89</v>
+      </c>
+      <c r="O118">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>74</v>
+      </c>
+      <c r="C119" t="s">
+        <v>136</v>
+      </c>
+      <c r="D119" t="s">
+        <v>138</v>
+      </c>
+      <c r="E119" t="s">
+        <v>140</v>
+      </c>
+      <c r="F119">
+        <v>48</v>
+      </c>
+      <c r="G119">
+        <v>11</v>
+      </c>
+      <c r="H119">
+        <v>1572.33</v>
+      </c>
+      <c r="I119">
+        <v>4.023</v>
+      </c>
+      <c r="J119">
+        <v>5595.18</v>
+      </c>
+      <c r="K119">
+        <v>8.58</v>
+      </c>
+      <c r="L119">
+        <v>64827</v>
+      </c>
+      <c r="M119">
+        <v>44100</v>
+      </c>
+      <c r="N119">
+        <v>128</v>
+      </c>
+      <c r="O119">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>74</v>
+      </c>
+      <c r="C120" t="s">
+        <v>137</v>
+      </c>
+      <c r="D120" t="s">
+        <v>139</v>
+      </c>
+      <c r="E120" t="s">
+        <v>141</v>
+      </c>
+      <c r="F120">
+        <v>48</v>
+      </c>
+      <c r="G120">
+        <v>11</v>
+      </c>
+      <c r="H120">
+        <v>2403.33</v>
+      </c>
+      <c r="I120">
+        <v>3.499</v>
+      </c>
+      <c r="J120">
+        <v>5902.02</v>
+      </c>
+      <c r="K120">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="L120">
+        <v>154336</v>
+      </c>
+      <c r="M120">
+        <v>22050</v>
+      </c>
+      <c r="N120">
+        <v>352.9</v>
+      </c>
+      <c r="O120">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>75</v>
+      </c>
+      <c r="C121" t="s">
+        <v>136</v>
+      </c>
+      <c r="D121" t="s">
+        <v>138</v>
+      </c>
+      <c r="E121" t="s">
+        <v>140</v>
+      </c>
+      <c r="F121">
+        <v>24</v>
+      </c>
+      <c r="G121">
+        <v>6</v>
+      </c>
+      <c r="H121">
+        <v>1927.79</v>
+      </c>
+      <c r="I121">
+        <v>1.75</v>
+      </c>
+      <c r="J121">
+        <v>3677.99</v>
+      </c>
+      <c r="K121">
+        <v>6.53</v>
+      </c>
+      <c r="L121">
+        <v>28465</v>
+      </c>
+      <c r="M121">
+        <v>44100</v>
+      </c>
+      <c r="N121">
+        <v>128</v>
+      </c>
+      <c r="O121">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>75</v>
+      </c>
+      <c r="C122" t="s">
+        <v>137</v>
+      </c>
+      <c r="D122" t="s">
+        <v>139</v>
+      </c>
+      <c r="E122" t="s">
+        <v>141</v>
+      </c>
+      <c r="F122">
+        <v>24</v>
+      </c>
+      <c r="G122">
+        <v>6</v>
+      </c>
+      <c r="H122">
+        <v>7275.01</v>
+      </c>
+      <c r="I122">
+        <v>2.901</v>
+      </c>
+      <c r="J122">
+        <v>10176.32</v>
+      </c>
+      <c r="K122">
+        <v>2.36</v>
+      </c>
+      <c r="L122">
+        <v>127992</v>
+      </c>
+      <c r="M122">
+        <v>22050</v>
+      </c>
+      <c r="N122">
+        <v>352.92</v>
+      </c>
+      <c r="O122">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>76</v>
+      </c>
+      <c r="C123" t="s">
+        <v>136</v>
+      </c>
+      <c r="D123" t="s">
+        <v>138</v>
+      </c>
+      <c r="E123" t="s">
+        <v>140</v>
+      </c>
+      <c r="F123">
+        <v>25</v>
+      </c>
+      <c r="G123">
+        <v>6</v>
+      </c>
+      <c r="H123">
+        <v>1855.61</v>
+      </c>
+      <c r="I123">
+        <v>2.403</v>
+      </c>
+      <c r="J123">
+        <v>4258.88</v>
+      </c>
+      <c r="K123">
+        <v>5.87</v>
+      </c>
+      <c r="L123">
+        <v>38914</v>
+      </c>
+      <c r="M123">
+        <v>44100</v>
+      </c>
+      <c r="N123">
+        <v>128</v>
+      </c>
+      <c r="O123">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>76</v>
+      </c>
+      <c r="C124" t="s">
+        <v>137</v>
+      </c>
+      <c r="D124" t="s">
+        <v>139</v>
+      </c>
+      <c r="E124" t="s">
+        <v>141</v>
+      </c>
+      <c r="F124">
+        <v>25</v>
+      </c>
+      <c r="G124">
+        <v>6</v>
+      </c>
+      <c r="H124">
+        <v>1851.52</v>
+      </c>
+      <c r="I124">
+        <v>2.304</v>
+      </c>
+      <c r="J124">
+        <v>4155.51</v>
+      </c>
+      <c r="K124">
+        <v>6.02</v>
+      </c>
+      <c r="L124">
+        <v>101650</v>
+      </c>
+      <c r="M124">
+        <v>22050</v>
+      </c>
+      <c r="N124">
+        <v>352.95</v>
+      </c>
+      <c r="O124">
+        <v>0.0375</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>77</v>
+      </c>
+      <c r="C125" t="s">
+        <v>136</v>
+      </c>
+      <c r="D125" t="s">
+        <v>138</v>
+      </c>
+      <c r="E125" t="s">
+        <v>140</v>
+      </c>
+      <c r="F125">
+        <v>56</v>
+      </c>
+      <c r="G125">
+        <v>13</v>
+      </c>
+      <c r="H125">
+        <v>1473.84</v>
+      </c>
+      <c r="I125">
+        <v>3.37</v>
+      </c>
+      <c r="J125">
+        <v>4843.64</v>
+      </c>
+      <c r="K125">
+        <v>11.56</v>
+      </c>
+      <c r="L125">
+        <v>54378</v>
+      </c>
+      <c r="M125">
+        <v>44100</v>
+      </c>
+      <c r="N125">
+        <v>128</v>
+      </c>
+      <c r="O125">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>77</v>
+      </c>
+      <c r="C126" t="s">
+        <v>137</v>
+      </c>
+      <c r="D126" t="s">
+        <v>139</v>
+      </c>
+      <c r="E126" t="s">
+        <v>141</v>
+      </c>
+      <c r="F126">
+        <v>56</v>
+      </c>
+      <c r="G126">
+        <v>13</v>
+      </c>
+      <c r="H126">
+        <v>2488.81</v>
+      </c>
+      <c r="I126">
+        <v>4.011</v>
+      </c>
+      <c r="J126">
+        <v>6499.47</v>
+      </c>
+      <c r="K126">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="L126">
+        <v>176914</v>
+      </c>
+      <c r="M126">
+        <v>22050</v>
+      </c>
+      <c r="N126">
+        <v>352.89</v>
+      </c>
+      <c r="O126">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>78</v>
+      </c>
+      <c r="C127" t="s">
+        <v>136</v>
+      </c>
+      <c r="D127" t="s">
+        <v>138</v>
+      </c>
+      <c r="E127" t="s">
+        <v>140</v>
+      </c>
+      <c r="F127">
+        <v>37</v>
+      </c>
+      <c r="G127">
+        <v>9</v>
+      </c>
+      <c r="H127">
+        <v>1583.7</v>
+      </c>
+      <c r="I127">
+        <v>2.769</v>
+      </c>
+      <c r="J127">
+        <v>4352.68</v>
+      </c>
+      <c r="K127">
+        <v>8.5</v>
+      </c>
+      <c r="L127">
+        <v>44765</v>
+      </c>
+      <c r="M127">
+        <v>44100</v>
+      </c>
+      <c r="N127">
+        <v>128</v>
+      </c>
+      <c r="O127">
+        <v>0.148</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>78</v>
+      </c>
+      <c r="C128" t="s">
+        <v>137</v>
+      </c>
+      <c r="D128" t="s">
+        <v>139</v>
+      </c>
+      <c r="E128" t="s">
+        <v>141</v>
+      </c>
+      <c r="F128">
+        <v>37</v>
+      </c>
+      <c r="G128">
+        <v>9</v>
+      </c>
+      <c r="H128">
+        <v>3201.45</v>
+      </c>
+      <c r="I128">
+        <v>3.755</v>
+      </c>
+      <c r="J128">
+        <v>6956.09</v>
+      </c>
+      <c r="K128">
+        <v>5.32</v>
+      </c>
+      <c r="L128">
+        <v>165624</v>
+      </c>
+      <c r="M128">
+        <v>22050</v>
+      </c>
+      <c r="N128">
+        <v>352.89</v>
+      </c>
+      <c r="O128">
+        <v>0.0555</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>79</v>
+      </c>
+      <c r="C129" t="s">
+        <v>136</v>
+      </c>
+      <c r="D129" t="s">
+        <v>138</v>
+      </c>
+      <c r="E129" t="s">
+        <v>140</v>
+      </c>
+      <c r="F129">
+        <v>39</v>
+      </c>
+      <c r="G129">
+        <v>9</v>
+      </c>
+      <c r="H129">
+        <v>2059.87</v>
+      </c>
+      <c r="I129">
+        <v>2.638</v>
+      </c>
+      <c r="J129">
+        <v>4698.24</v>
+      </c>
+      <c r="K129">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L129">
+        <v>42675</v>
+      </c>
+      <c r="M129">
+        <v>44100</v>
+      </c>
+      <c r="N129">
+        <v>128</v>
+      </c>
+      <c r="O129">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>79</v>
+      </c>
+      <c r="C130" t="s">
+        <v>137</v>
+      </c>
+      <c r="D130" t="s">
+        <v>139</v>
+      </c>
+      <c r="E130" t="s">
+        <v>141</v>
+      </c>
+      <c r="F130">
+        <v>39</v>
+      </c>
+      <c r="G130">
+        <v>9</v>
+      </c>
+      <c r="H130">
+        <v>6029.44</v>
+      </c>
+      <c r="I130">
+        <v>3.584</v>
+      </c>
+      <c r="J130">
+        <v>9613.43</v>
+      </c>
+      <c r="K130">
+        <v>4.06</v>
+      </c>
+      <c r="L130">
+        <v>158098</v>
+      </c>
+      <c r="M130">
+        <v>22050</v>
+      </c>
+      <c r="N130">
+        <v>352.9</v>
+      </c>
+      <c r="O130">
+        <v>0.0585</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>80</v>
+      </c>
+      <c r="C131" t="s">
+        <v>136</v>
+      </c>
+      <c r="D131" t="s">
+        <v>138</v>
+      </c>
+      <c r="E131" t="s">
+        <v>140</v>
+      </c>
+      <c r="F131">
+        <v>64</v>
+      </c>
+      <c r="G131">
+        <v>15</v>
+      </c>
+      <c r="H131">
+        <v>1928.59</v>
+      </c>
+      <c r="I131">
+        <v>5.251</v>
+      </c>
+      <c r="J131">
+        <v>7179.2</v>
+      </c>
+      <c r="K131">
+        <v>8.91</v>
+      </c>
+      <c r="L131">
+        <v>84471</v>
+      </c>
+      <c r="M131">
+        <v>44100</v>
+      </c>
+      <c r="N131">
+        <v>128</v>
+      </c>
+      <c r="O131">
+        <v>0.256</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>80</v>
+      </c>
+      <c r="C132" t="s">
+        <v>137</v>
+      </c>
+      <c r="D132" t="s">
+        <v>139</v>
+      </c>
+      <c r="E132" t="s">
+        <v>141</v>
+      </c>
+      <c r="F132">
+        <v>64</v>
+      </c>
+      <c r="G132">
+        <v>15</v>
+      </c>
+      <c r="H132">
+        <v>3125.16</v>
+      </c>
+      <c r="I132">
+        <v>4.864</v>
+      </c>
+      <c r="J132">
+        <v>7989.15</v>
+      </c>
+      <c r="K132">
+        <v>8.01</v>
+      </c>
+      <c r="L132">
+        <v>214546</v>
+      </c>
+      <c r="M132">
+        <v>22050</v>
+      </c>
+      <c r="N132">
+        <v>352.87</v>
+      </c>
+      <c r="O132">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>81</v>
+      </c>
+      <c r="C133" t="s">
+        <v>136</v>
+      </c>
+      <c r="D133" t="s">
+        <v>138</v>
+      </c>
+      <c r="E133" t="s">
+        <v>140</v>
+      </c>
+      <c r="F133">
+        <v>31</v>
+      </c>
+      <c r="G133">
+        <v>6</v>
+      </c>
+      <c r="H133">
+        <v>1267.65</v>
+      </c>
+      <c r="I133">
+        <v>1.802</v>
+      </c>
+      <c r="J133">
+        <v>3070.1</v>
+      </c>
+      <c r="K133">
+        <v>10.1</v>
+      </c>
+      <c r="L133">
+        <v>29301</v>
+      </c>
+      <c r="M133">
+        <v>44100</v>
+      </c>
+      <c r="N133">
+        <v>128</v>
+      </c>
+      <c r="O133">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>81</v>
+      </c>
+      <c r="C134" t="s">
+        <v>137</v>
+      </c>
+      <c r="D134" t="s">
+        <v>139</v>
+      </c>
+      <c r="E134" t="s">
+        <v>141</v>
+      </c>
+      <c r="F134">
+        <v>31</v>
+      </c>
+      <c r="G134">
+        <v>6</v>
+      </c>
+      <c r="H134">
+        <v>1599.07</v>
+      </c>
+      <c r="I134">
+        <v>2.133</v>
+      </c>
+      <c r="J134">
+        <v>3732.4</v>
+      </c>
+      <c r="K134">
+        <v>8.31</v>
+      </c>
+      <c r="L134">
+        <v>94124</v>
+      </c>
+      <c r="M134">
+        <v>22050</v>
+      </c>
+      <c r="N134">
+        <v>352.96</v>
+      </c>
+      <c r="O134">
+        <v>0.0465</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>82</v>
+      </c>
+      <c r="C135" t="s">
+        <v>136</v>
+      </c>
+      <c r="D135" t="s">
+        <v>138</v>
+      </c>
+      <c r="E135" t="s">
+        <v>140</v>
+      </c>
+      <c r="F135">
+        <v>52</v>
+      </c>
+      <c r="G135">
+        <v>13</v>
+      </c>
+      <c r="H135">
+        <v>1449.49</v>
+      </c>
+      <c r="I135">
+        <v>3.37</v>
+      </c>
+      <c r="J135">
+        <v>4819.29</v>
+      </c>
+      <c r="K135">
+        <v>10.79</v>
+      </c>
+      <c r="L135">
+        <v>54378</v>
+      </c>
+      <c r="M135">
+        <v>44100</v>
+      </c>
+      <c r="N135">
+        <v>128</v>
+      </c>
+      <c r="O135">
+        <v>0.208</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>82</v>
+      </c>
+      <c r="C136" t="s">
+        <v>137</v>
+      </c>
+      <c r="D136" t="s">
+        <v>139</v>
+      </c>
+      <c r="E136" t="s">
+        <v>141</v>
+      </c>
+      <c r="F136">
+        <v>52</v>
+      </c>
+      <c r="G136">
+        <v>13</v>
+      </c>
+      <c r="H136">
+        <v>2276.6</v>
+      </c>
+      <c r="I136">
+        <v>3.84</v>
+      </c>
+      <c r="J136">
+        <v>6116.6</v>
+      </c>
+      <c r="K136">
+        <v>8.5</v>
+      </c>
+      <c r="L136">
+        <v>169388</v>
+      </c>
+      <c r="M136">
+        <v>22050</v>
+      </c>
+      <c r="N136">
+        <v>352.89</v>
+      </c>
+      <c r="O136">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>83</v>
+      </c>
+      <c r="C137" t="s">
+        <v>136</v>
+      </c>
+      <c r="D137" t="s">
+        <v>138</v>
+      </c>
+      <c r="E137" t="s">
+        <v>140</v>
+      </c>
+      <c r="F137">
+        <v>33</v>
+      </c>
+      <c r="G137">
+        <v>8</v>
+      </c>
+      <c r="H137">
+        <v>1610.47</v>
+      </c>
+      <c r="I137">
+        <v>2.456</v>
+      </c>
+      <c r="J137">
+        <v>4065.98</v>
+      </c>
+      <c r="K137">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="L137">
+        <v>39750</v>
+      </c>
+      <c r="M137">
+        <v>44100</v>
+      </c>
+      <c r="N137">
+        <v>128</v>
+      </c>
+      <c r="O137">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>83</v>
+      </c>
+      <c r="C138" t="s">
+        <v>137</v>
+      </c>
+      <c r="D138" t="s">
+        <v>139</v>
+      </c>
+      <c r="E138" t="s">
+        <v>141</v>
+      </c>
+      <c r="F138">
+        <v>33</v>
+      </c>
+      <c r="G138">
+        <v>8</v>
+      </c>
+      <c r="H138">
+        <v>1485.42</v>
+      </c>
+      <c r="I138">
+        <v>2.219</v>
+      </c>
+      <c r="J138">
+        <v>3704.1</v>
+      </c>
+      <c r="K138">
+        <v>8.91</v>
+      </c>
+      <c r="L138">
+        <v>97888</v>
+      </c>
+      <c r="M138">
+        <v>22050</v>
+      </c>
+      <c r="N138">
+        <v>352.96</v>
+      </c>
+      <c r="O138">
+        <v>0.0495</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>84</v>
+      </c>
+      <c r="C139" t="s">
+        <v>136</v>
+      </c>
+      <c r="D139" t="s">
+        <v>138</v>
+      </c>
+      <c r="E139" t="s">
+        <v>140</v>
+      </c>
+      <c r="F139">
+        <v>48</v>
+      </c>
+      <c r="G139">
+        <v>10</v>
+      </c>
+      <c r="H139">
+        <v>1491.09</v>
+      </c>
+      <c r="I139">
+        <v>4.127</v>
+      </c>
+      <c r="J139">
+        <v>5618.44</v>
+      </c>
+      <c r="K139">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="L139">
+        <v>66499</v>
+      </c>
+      <c r="M139">
+        <v>44100</v>
+      </c>
+      <c r="N139">
+        <v>128</v>
+      </c>
+      <c r="O139">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>84</v>
+      </c>
+      <c r="C140" t="s">
+        <v>137</v>
+      </c>
+      <c r="D140" t="s">
+        <v>139</v>
+      </c>
+      <c r="E140" t="s">
+        <v>141</v>
+      </c>
+      <c r="F140">
+        <v>48</v>
+      </c>
+      <c r="G140">
+        <v>10</v>
+      </c>
+      <c r="H140">
+        <v>2156.65</v>
+      </c>
+      <c r="I140">
+        <v>3.669</v>
+      </c>
+      <c r="J140">
+        <v>5825.99</v>
+      </c>
+      <c r="K140">
+        <v>8.24</v>
+      </c>
+      <c r="L140">
+        <v>161862</v>
+      </c>
+      <c r="M140">
+        <v>22050</v>
+      </c>
+      <c r="N140">
+        <v>352.9</v>
+      </c>
+      <c r="O140">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>85</v>
+      </c>
+      <c r="C141" t="s">
+        <v>136</v>
+      </c>
+      <c r="D141" t="s">
+        <v>138</v>
+      </c>
+      <c r="E141" t="s">
+        <v>140</v>
+      </c>
+      <c r="F141">
+        <v>33</v>
+      </c>
+      <c r="G141">
+        <v>8</v>
+      </c>
+      <c r="H141">
+        <v>1328.76</v>
+      </c>
+      <c r="I141">
+        <v>2.534</v>
+      </c>
+      <c r="J141">
+        <v>3862.64</v>
+      </c>
+      <c r="K141">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="L141">
+        <v>41004</v>
+      </c>
+      <c r="M141">
+        <v>44100</v>
+      </c>
+      <c r="N141">
+        <v>128</v>
+      </c>
+      <c r="O141">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>85</v>
+      </c>
+      <c r="C142" t="s">
+        <v>137</v>
+      </c>
+      <c r="D142" t="s">
+        <v>139</v>
+      </c>
+      <c r="E142" t="s">
+        <v>141</v>
+      </c>
+      <c r="F142">
+        <v>33</v>
+      </c>
+      <c r="G142">
+        <v>8</v>
+      </c>
+      <c r="H142">
+        <v>2686.58</v>
+      </c>
+      <c r="I142">
+        <v>2.816</v>
+      </c>
+      <c r="J142">
+        <v>5502.59</v>
+      </c>
+      <c r="K142">
+        <v>6</v>
+      </c>
+      <c r="L142">
+        <v>124230</v>
+      </c>
+      <c r="M142">
+        <v>22050</v>
+      </c>
+      <c r="N142">
+        <v>352.92</v>
+      </c>
+      <c r="O142">
+        <v>0.0495</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>86</v>
+      </c>
+      <c r="C143" t="s">
+        <v>136</v>
+      </c>
+      <c r="D143" t="s">
+        <v>138</v>
+      </c>
+      <c r="E143" t="s">
+        <v>140</v>
+      </c>
+      <c r="F143">
+        <v>130</v>
+      </c>
+      <c r="G143">
+        <v>28</v>
+      </c>
+      <c r="H143">
+        <v>3192.44</v>
+      </c>
+      <c r="I143">
+        <v>8.907999999999999</v>
+      </c>
+      <c r="J143">
+        <v>12100.2</v>
+      </c>
+      <c r="K143">
+        <v>10.74</v>
+      </c>
+      <c r="L143">
+        <v>142986</v>
+      </c>
+      <c r="M143">
+        <v>44100</v>
+      </c>
+      <c r="N143">
+        <v>128</v>
+      </c>
+      <c r="O143">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>86</v>
+      </c>
+      <c r="C144" t="s">
+        <v>137</v>
+      </c>
+      <c r="D144" t="s">
+        <v>139</v>
+      </c>
+      <c r="E144" t="s">
+        <v>141</v>
+      </c>
+      <c r="F144">
+        <v>130</v>
+      </c>
+      <c r="G144">
+        <v>28</v>
+      </c>
+      <c r="H144">
+        <v>7255.97</v>
+      </c>
+      <c r="I144">
+        <v>8.532999999999999</v>
+      </c>
+      <c r="J144">
+        <v>15789.3</v>
+      </c>
+      <c r="K144">
+        <v>8.23</v>
+      </c>
+      <c r="L144">
+        <v>376364</v>
+      </c>
+      <c r="M144">
+        <v>22050</v>
+      </c>
+      <c r="N144">
+        <v>352.84</v>
+      </c>
+      <c r="O144">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>87</v>
+      </c>
+      <c r="C145" t="s">
+        <v>136</v>
+      </c>
+      <c r="D145" t="s">
+        <v>138</v>
+      </c>
+      <c r="E145" t="s">
+        <v>140</v>
+      </c>
+      <c r="F145">
+        <v>43</v>
+      </c>
+      <c r="G145">
+        <v>10</v>
+      </c>
+      <c r="H145">
+        <v>2628.52</v>
+      </c>
+      <c r="I145">
+        <v>2.926</v>
+      </c>
+      <c r="J145">
+        <v>5554.23</v>
+      </c>
+      <c r="K145">
+        <v>7.74</v>
+      </c>
+      <c r="L145">
+        <v>47273</v>
+      </c>
+      <c r="M145">
+        <v>44100</v>
+      </c>
+      <c r="N145">
+        <v>128</v>
+      </c>
+      <c r="O145">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>87</v>
+      </c>
+      <c r="C146" t="s">
+        <v>137</v>
+      </c>
+      <c r="D146" t="s">
+        <v>139</v>
+      </c>
+      <c r="E146" t="s">
+        <v>141</v>
+      </c>
+      <c r="F146">
+        <v>43</v>
+      </c>
+      <c r="G146">
+        <v>10</v>
+      </c>
+      <c r="H146">
+        <v>6425.01</v>
+      </c>
+      <c r="I146">
+        <v>3.84</v>
+      </c>
+      <c r="J146">
+        <v>10265.01</v>
+      </c>
+      <c r="K146">
+        <v>4.19</v>
+      </c>
+      <c r="L146">
+        <v>169388</v>
+      </c>
+      <c r="M146">
+        <v>22050</v>
+      </c>
+      <c r="N146">
+        <v>352.89</v>
+      </c>
+      <c r="O146">
+        <v>0.0645</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>88</v>
+      </c>
+      <c r="C147" t="s">
+        <v>136</v>
+      </c>
+      <c r="D147" t="s">
+        <v>138</v>
+      </c>
+      <c r="E147" t="s">
+        <v>140</v>
+      </c>
+      <c r="F147">
+        <v>40</v>
+      </c>
+      <c r="G147">
+        <v>9</v>
+      </c>
+      <c r="H147">
+        <v>4675.16</v>
+      </c>
+      <c r="I147">
+        <v>2.743</v>
+      </c>
+      <c r="J147">
+        <v>7418.02</v>
+      </c>
+      <c r="K147">
+        <v>5.39</v>
+      </c>
+      <c r="L147">
+        <v>44347</v>
+      </c>
+      <c r="M147">
+        <v>44100</v>
+      </c>
+      <c r="N147">
+        <v>128</v>
+      </c>
+      <c r="O147">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>88</v>
+      </c>
+      <c r="C148" t="s">
+        <v>137</v>
+      </c>
+      <c r="D148" t="s">
+        <v>139</v>
+      </c>
+      <c r="E148" t="s">
+        <v>141</v>
+      </c>
+      <c r="F148">
+        <v>40</v>
+      </c>
+      <c r="G148">
+        <v>9</v>
+      </c>
+      <c r="H148">
+        <v>3512.87</v>
+      </c>
+      <c r="I148">
+        <v>4.181</v>
+      </c>
+      <c r="J148">
+        <v>7694.19</v>
+      </c>
+      <c r="K148">
+        <v>5.2</v>
+      </c>
+      <c r="L148">
+        <v>184440</v>
+      </c>
+      <c r="M148">
+        <v>22050</v>
+      </c>
+      <c r="N148">
+        <v>352.88</v>
+      </c>
+      <c r="O148">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>89</v>
+      </c>
+      <c r="C149" t="s">
+        <v>136</v>
+      </c>
+      <c r="D149" t="s">
+        <v>138</v>
+      </c>
+      <c r="E149" t="s">
+        <v>140</v>
+      </c>
+      <c r="F149">
+        <v>47</v>
+      </c>
+      <c r="G149">
+        <v>9</v>
+      </c>
+      <c r="H149">
+        <v>1274.39</v>
+      </c>
+      <c r="I149">
+        <v>3.579</v>
+      </c>
+      <c r="J149">
+        <v>4853.16</v>
+      </c>
+      <c r="K149">
+        <v>9.68</v>
+      </c>
+      <c r="L149">
+        <v>57722</v>
+      </c>
+      <c r="M149">
+        <v>44100</v>
+      </c>
+      <c r="N149">
+        <v>128</v>
+      </c>
+      <c r="O149">
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>89</v>
+      </c>
+      <c r="C150" t="s">
+        <v>137</v>
+      </c>
+      <c r="D150" t="s">
+        <v>139</v>
+      </c>
+      <c r="E150" t="s">
+        <v>141</v>
+      </c>
+      <c r="F150">
+        <v>47</v>
+      </c>
+      <c r="G150">
+        <v>9</v>
+      </c>
+      <c r="H150">
+        <v>5064.82</v>
+      </c>
+      <c r="I150">
+        <v>3.925</v>
+      </c>
+      <c r="J150">
+        <v>8990.17</v>
+      </c>
+      <c r="K150">
+        <v>5.23</v>
+      </c>
+      <c r="L150">
+        <v>173152</v>
+      </c>
+      <c r="M150">
+        <v>22050</v>
+      </c>
+      <c r="N150">
+        <v>352.89</v>
+      </c>
+      <c r="O150">
+        <v>0.07049999999999999</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>90</v>
+      </c>
+      <c r="C151" t="s">
+        <v>136</v>
+      </c>
+      <c r="D151" t="s">
+        <v>138</v>
+      </c>
+      <c r="E151" t="s">
+        <v>140</v>
+      </c>
+      <c r="F151">
+        <v>19</v>
+      </c>
+      <c r="G151">
+        <v>5</v>
+      </c>
+      <c r="H151">
+        <v>1301.44</v>
+      </c>
+      <c r="I151">
+        <v>1.567</v>
+      </c>
+      <c r="J151">
+        <v>2868.79</v>
+      </c>
+      <c r="K151">
+        <v>6.62</v>
+      </c>
+      <c r="L151">
+        <v>25539</v>
+      </c>
+      <c r="M151">
+        <v>44100</v>
+      </c>
+      <c r="N151">
+        <v>128</v>
+      </c>
+      <c r="O151">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>90</v>
+      </c>
+      <c r="C152" t="s">
+        <v>137</v>
+      </c>
+      <c r="D152" t="s">
+        <v>139</v>
+      </c>
+      <c r="E152" t="s">
+        <v>141</v>
+      </c>
+      <c r="F152">
+        <v>19</v>
+      </c>
+      <c r="G152">
+        <v>5</v>
+      </c>
+      <c r="H152">
+        <v>1411.31</v>
+      </c>
+      <c r="I152">
+        <v>1.792</v>
+      </c>
+      <c r="J152">
+        <v>3203.33</v>
+      </c>
+      <c r="K152">
+        <v>5.93</v>
+      </c>
+      <c r="L152">
+        <v>79072</v>
+      </c>
+      <c r="M152">
+        <v>22050</v>
+      </c>
+      <c r="N152">
+        <v>353</v>
+      </c>
+      <c r="O152">
+        <v>0.0285</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>91</v>
+      </c>
+      <c r="C153" t="s">
+        <v>136</v>
+      </c>
+      <c r="D153" t="s">
+        <v>138</v>
+      </c>
+      <c r="E153" t="s">
+        <v>140</v>
+      </c>
+      <c r="F153">
+        <v>38</v>
+      </c>
+      <c r="G153">
+        <v>8</v>
+      </c>
+      <c r="H153">
+        <v>1348.49</v>
+      </c>
+      <c r="I153">
+        <v>3.056</v>
+      </c>
+      <c r="J153">
+        <v>4404.82</v>
+      </c>
+      <c r="K153">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L153">
+        <v>49363</v>
+      </c>
+      <c r="M153">
+        <v>44100</v>
+      </c>
+      <c r="N153">
+        <v>128</v>
+      </c>
+      <c r="O153">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>91</v>
+      </c>
+      <c r="C154" t="s">
+        <v>137</v>
+      </c>
+      <c r="D154" t="s">
+        <v>139</v>
+      </c>
+      <c r="E154" t="s">
+        <v>141</v>
+      </c>
+      <c r="F154">
+        <v>38</v>
+      </c>
+      <c r="G154">
+        <v>8</v>
+      </c>
+      <c r="H154">
+        <v>7474.33</v>
+      </c>
+      <c r="I154">
+        <v>3.157</v>
+      </c>
+      <c r="J154">
+        <v>10631.66</v>
+      </c>
+      <c r="K154">
+        <v>3.57</v>
+      </c>
+      <c r="L154">
+        <v>139282</v>
+      </c>
+      <c r="M154">
+        <v>22050</v>
+      </c>
+      <c r="N154">
+        <v>352.91</v>
+      </c>
+      <c r="O154">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>92</v>
+      </c>
+      <c r="C155" t="s">
+        <v>136</v>
+      </c>
+      <c r="D155" t="s">
+        <v>138</v>
+      </c>
+      <c r="E155" t="s">
+        <v>140</v>
+      </c>
+      <c r="F155">
+        <v>48</v>
+      </c>
+      <c r="G155">
+        <v>11</v>
+      </c>
+      <c r="H155">
+        <v>4044.42</v>
+      </c>
+      <c r="I155">
+        <v>3.605</v>
+      </c>
+      <c r="J155">
+        <v>7649.32</v>
+      </c>
+      <c r="K155">
+        <v>6.28</v>
+      </c>
+      <c r="L155">
+        <v>58140</v>
+      </c>
+      <c r="M155">
+        <v>44100</v>
+      </c>
+      <c r="N155">
+        <v>128</v>
+      </c>
+      <c r="O155">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>92</v>
+      </c>
+      <c r="C156" t="s">
+        <v>137</v>
+      </c>
+      <c r="D156" t="s">
+        <v>139</v>
+      </c>
+      <c r="E156" t="s">
+        <v>141</v>
+      </c>
+      <c r="F156">
+        <v>48</v>
+      </c>
+      <c r="G156">
+        <v>11</v>
+      </c>
+      <c r="H156">
+        <v>3336.96</v>
+      </c>
+      <c r="I156">
+        <v>4.181</v>
+      </c>
+      <c r="J156">
+        <v>7518.28</v>
+      </c>
+      <c r="K156">
+        <v>6.38</v>
+      </c>
+      <c r="L156">
+        <v>184440</v>
+      </c>
+      <c r="M156">
+        <v>22050</v>
+      </c>
+      <c r="N156">
+        <v>352.88</v>
+      </c>
+      <c r="O156">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>93</v>
+      </c>
+      <c r="C157" t="s">
+        <v>136</v>
+      </c>
+      <c r="D157" t="s">
+        <v>138</v>
+      </c>
+      <c r="E157" t="s">
+        <v>140</v>
+      </c>
+      <c r="F157">
+        <v>35</v>
+      </c>
+      <c r="G157">
+        <v>8</v>
+      </c>
+      <c r="H157">
+        <v>2374.15</v>
+      </c>
+      <c r="I157">
+        <v>2.926</v>
+      </c>
+      <c r="J157">
+        <v>5299.87</v>
+      </c>
+      <c r="K157">
+        <v>6.6</v>
+      </c>
+      <c r="L157">
+        <v>47273</v>
+      </c>
+      <c r="M157">
+        <v>44100</v>
+      </c>
+      <c r="N157">
+        <v>128</v>
+      </c>
+      <c r="O157">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>93</v>
+      </c>
+      <c r="C158" t="s">
+        <v>137</v>
+      </c>
+      <c r="D158" t="s">
+        <v>139</v>
+      </c>
+      <c r="E158" t="s">
+        <v>141</v>
+      </c>
+      <c r="F158">
+        <v>35</v>
+      </c>
+      <c r="G158">
+        <v>8</v>
+      </c>
+      <c r="H158">
+        <v>2767.15</v>
+      </c>
+      <c r="I158">
+        <v>3.072</v>
+      </c>
+      <c r="J158">
+        <v>5839.17</v>
+      </c>
+      <c r="K158">
+        <v>5.99</v>
+      </c>
+      <c r="L158">
+        <v>135520</v>
+      </c>
+      <c r="M158">
+        <v>22050</v>
+      </c>
+      <c r="N158">
+        <v>352.91</v>
+      </c>
+      <c r="O158">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>94</v>
+      </c>
+      <c r="C159" t="s">
+        <v>136</v>
+      </c>
+      <c r="D159" t="s">
+        <v>138</v>
+      </c>
+      <c r="E159" t="s">
+        <v>140</v>
+      </c>
+      <c r="F159">
+        <v>33</v>
+      </c>
+      <c r="G159">
+        <v>8</v>
+      </c>
+      <c r="H159">
+        <v>1460.56</v>
+      </c>
+      <c r="I159">
+        <v>2.638</v>
+      </c>
+      <c r="J159">
+        <v>4098.92</v>
+      </c>
+      <c r="K159">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="L159">
+        <v>42675</v>
+      </c>
+      <c r="M159">
+        <v>44100</v>
+      </c>
+      <c r="N159">
+        <v>128</v>
+      </c>
+      <c r="O159">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>94</v>
+      </c>
+      <c r="C160" t="s">
+        <v>137</v>
+      </c>
+      <c r="D160" t="s">
+        <v>139</v>
+      </c>
+      <c r="E160" t="s">
+        <v>141</v>
+      </c>
+      <c r="F160">
+        <v>33</v>
+      </c>
+      <c r="G160">
+        <v>8</v>
+      </c>
+      <c r="H160">
+        <v>2026.05</v>
+      </c>
+      <c r="I160">
+        <v>3.669</v>
+      </c>
+      <c r="J160">
+        <v>5695.39</v>
+      </c>
+      <c r="K160">
+        <v>5.79</v>
+      </c>
+      <c r="L160">
+        <v>161862</v>
+      </c>
+      <c r="M160">
+        <v>22050</v>
+      </c>
+      <c r="N160">
+        <v>352.9</v>
+      </c>
+      <c r="O160">
+        <v>0.0495</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>95</v>
+      </c>
+      <c r="C161" t="s">
+        <v>136</v>
+      </c>
+      <c r="D161" t="s">
+        <v>138</v>
+      </c>
+      <c r="E161" t="s">
+        <v>140</v>
+      </c>
+      <c r="F161">
+        <v>45</v>
+      </c>
+      <c r="G161">
+        <v>9</v>
+      </c>
+      <c r="H161">
+        <v>1538.51</v>
+      </c>
+      <c r="I161">
+        <v>4.023</v>
+      </c>
+      <c r="J161">
+        <v>5561.37</v>
+      </c>
+      <c r="K161">
+        <v>8.09</v>
+      </c>
+      <c r="L161">
+        <v>64827</v>
+      </c>
+      <c r="M161">
+        <v>44100</v>
+      </c>
+      <c r="N161">
+        <v>128</v>
+      </c>
+      <c r="O161">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>95</v>
+      </c>
+      <c r="C162" t="s">
+        <v>137</v>
+      </c>
+      <c r="D162" t="s">
+        <v>139</v>
+      </c>
+      <c r="E162" t="s">
+        <v>141</v>
+      </c>
+      <c r="F162">
+        <v>45</v>
+      </c>
+      <c r="G162">
+        <v>9</v>
+      </c>
+      <c r="H162">
+        <v>2173.76</v>
+      </c>
+      <c r="I162">
+        <v>4.011</v>
+      </c>
+      <c r="J162">
+        <v>6184.42</v>
+      </c>
+      <c r="K162">
+        <v>7.28</v>
+      </c>
+      <c r="L162">
+        <v>176914</v>
+      </c>
+      <c r="M162">
+        <v>22050</v>
+      </c>
+      <c r="N162">
+        <v>352.89</v>
+      </c>
+      <c r="O162">
+        <v>0.0675</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>96</v>
+      </c>
+      <c r="C163" t="s">
+        <v>136</v>
+      </c>
+      <c r="D163" t="s">
+        <v>138</v>
+      </c>
+      <c r="E163" t="s">
+        <v>140</v>
+      </c>
+      <c r="F163">
+        <v>58</v>
+      </c>
+      <c r="G163">
+        <v>12</v>
+      </c>
+      <c r="H163">
+        <v>1345.07</v>
+      </c>
+      <c r="I163">
+        <v>3.187</v>
+      </c>
+      <c r="J163">
+        <v>4532.01</v>
+      </c>
+      <c r="K163">
+        <v>12.8</v>
+      </c>
+      <c r="L163">
+        <v>51453</v>
+      </c>
+      <c r="M163">
+        <v>44100</v>
+      </c>
+      <c r="N163">
+        <v>128</v>
+      </c>
+      <c r="O163">
+        <v>0.232</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>96</v>
+      </c>
+      <c r="C164" t="s">
+        <v>137</v>
+      </c>
+      <c r="D164" t="s">
+        <v>139</v>
+      </c>
+      <c r="E164" t="s">
+        <v>141</v>
+      </c>
+      <c r="F164">
+        <v>58</v>
+      </c>
+      <c r="G164">
+        <v>12</v>
+      </c>
+      <c r="H164">
+        <v>2426.77</v>
+      </c>
+      <c r="I164">
+        <v>3.925</v>
+      </c>
+      <c r="J164">
+        <v>6352.12</v>
+      </c>
+      <c r="K164">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="L164">
+        <v>173152</v>
+      </c>
+      <c r="M164">
+        <v>22050</v>
+      </c>
+      <c r="N164">
+        <v>352.89</v>
+      </c>
+      <c r="O164">
+        <v>0.08699999999999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>97</v>
+      </c>
+      <c r="C165" t="s">
+        <v>136</v>
+      </c>
+      <c r="D165" t="s">
+        <v>138</v>
+      </c>
+      <c r="E165" t="s">
+        <v>140</v>
+      </c>
+      <c r="F165">
+        <v>50</v>
+      </c>
+      <c r="G165">
+        <v>12</v>
+      </c>
+      <c r="H165">
+        <v>1345.87</v>
+      </c>
+      <c r="I165">
+        <v>3.291</v>
+      </c>
+      <c r="J165">
+        <v>4637.3</v>
+      </c>
+      <c r="K165">
+        <v>10.78</v>
+      </c>
+      <c r="L165">
+        <v>53124</v>
+      </c>
+      <c r="M165">
+        <v>44100</v>
+      </c>
+      <c r="N165">
+        <v>128</v>
+      </c>
+      <c r="O165">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>97</v>
+      </c>
+      <c r="C166" t="s">
+        <v>137</v>
+      </c>
+      <c r="D166" t="s">
+        <v>139</v>
+      </c>
+      <c r="E166" t="s">
+        <v>141</v>
+      </c>
+      <c r="F166">
+        <v>50</v>
+      </c>
+      <c r="G166">
+        <v>12</v>
+      </c>
+      <c r="H166">
+        <v>2731.88</v>
+      </c>
+      <c r="I166">
+        <v>5.035</v>
+      </c>
+      <c r="J166">
+        <v>7766.53</v>
+      </c>
+      <c r="K166">
+        <v>6.44</v>
+      </c>
+      <c r="L166">
+        <v>222072</v>
+      </c>
+      <c r="M166">
+        <v>22050</v>
+      </c>
+      <c r="N166">
+        <v>352.87</v>
+      </c>
+      <c r="O166">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>98</v>
+      </c>
+      <c r="C167" t="s">
+        <v>136</v>
+      </c>
+      <c r="D167" t="s">
+        <v>138</v>
+      </c>
+      <c r="E167" t="s">
+        <v>140</v>
+      </c>
+      <c r="F167">
+        <v>43</v>
+      </c>
+      <c r="G167">
+        <v>9</v>
+      </c>
+      <c r="H167">
+        <v>1523.71</v>
+      </c>
+      <c r="I167">
+        <v>3.344</v>
+      </c>
+      <c r="J167">
+        <v>4867.38</v>
+      </c>
+      <c r="K167">
+        <v>8.83</v>
+      </c>
+      <c r="L167">
+        <v>53960</v>
+      </c>
+      <c r="M167">
+        <v>44100</v>
+      </c>
+      <c r="N167">
+        <v>128</v>
+      </c>
+      <c r="O167">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>98</v>
+      </c>
+      <c r="C168" t="s">
+        <v>137</v>
+      </c>
+      <c r="D168" t="s">
+        <v>139</v>
+      </c>
+      <c r="E168" t="s">
+        <v>141</v>
+      </c>
+      <c r="F168">
+        <v>43</v>
+      </c>
+      <c r="G168">
+        <v>9</v>
+      </c>
+      <c r="H168">
+        <v>2284.13</v>
+      </c>
+      <c r="I168">
+        <v>3.584</v>
+      </c>
+      <c r="J168">
+        <v>5868.12</v>
+      </c>
+      <c r="K168">
+        <v>7.33</v>
+      </c>
+      <c r="L168">
+        <v>158098</v>
+      </c>
+      <c r="M168">
+        <v>22050</v>
+      </c>
+      <c r="N168">
+        <v>352.9</v>
+      </c>
+      <c r="O168">
+        <v>0.0645</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>99</v>
+      </c>
+      <c r="C169" t="s">
+        <v>136</v>
+      </c>
+      <c r="D169" t="s">
+        <v>138</v>
+      </c>
+      <c r="E169" t="s">
+        <v>140</v>
+      </c>
+      <c r="F169">
+        <v>32</v>
+      </c>
+      <c r="G169">
+        <v>8</v>
+      </c>
+      <c r="H169">
+        <v>1397.38</v>
+      </c>
+      <c r="I169">
+        <v>2.508</v>
+      </c>
+      <c r="J169">
+        <v>3905.14</v>
+      </c>
+      <c r="K169">
+        <v>8.19</v>
+      </c>
+      <c r="L169">
+        <v>40586</v>
+      </c>
+      <c r="M169">
+        <v>44100</v>
+      </c>
+      <c r="N169">
+        <v>128</v>
+      </c>
+      <c r="O169">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>99</v>
+      </c>
+      <c r="C170" t="s">
+        <v>137</v>
+      </c>
+      <c r="D170" t="s">
+        <v>139</v>
+      </c>
+      <c r="E170" t="s">
+        <v>141</v>
+      </c>
+      <c r="F170">
+        <v>32</v>
+      </c>
+      <c r="G170">
+        <v>8</v>
+      </c>
+      <c r="H170">
+        <v>3338.63</v>
+      </c>
+      <c r="I170">
+        <v>2.901</v>
+      </c>
+      <c r="J170">
+        <v>6239.94</v>
+      </c>
+      <c r="K170">
+        <v>5.13</v>
+      </c>
+      <c r="L170">
+        <v>127992</v>
+      </c>
+      <c r="M170">
+        <v>22050</v>
+      </c>
+      <c r="N170">
+        <v>352.92</v>
+      </c>
+      <c r="O170">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>100</v>
+      </c>
+      <c r="C171" t="s">
+        <v>136</v>
+      </c>
+      <c r="D171" t="s">
+        <v>138</v>
+      </c>
+      <c r="E171" t="s">
+        <v>140</v>
+      </c>
+      <c r="F171">
+        <v>42</v>
+      </c>
+      <c r="G171">
+        <v>8</v>
+      </c>
+      <c r="H171">
+        <v>1320.17</v>
+      </c>
+      <c r="I171">
+        <v>3.004</v>
+      </c>
+      <c r="J171">
+        <v>4324.25</v>
+      </c>
+      <c r="K171">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="L171">
+        <v>48527</v>
+      </c>
+      <c r="M171">
+        <v>44100</v>
+      </c>
+      <c r="N171">
+        <v>128</v>
+      </c>
+      <c r="O171">
+        <v>0.168</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>100</v>
+      </c>
+      <c r="C172" t="s">
+        <v>137</v>
+      </c>
+      <c r="D172" t="s">
+        <v>139</v>
+      </c>
+      <c r="E172" t="s">
+        <v>141</v>
+      </c>
+      <c r="F172">
+        <v>42</v>
+      </c>
+      <c r="G172">
+        <v>8</v>
+      </c>
+      <c r="H172">
+        <v>6786.36</v>
+      </c>
+      <c r="I172">
+        <v>4.181</v>
+      </c>
+      <c r="J172">
+        <v>10967.68</v>
+      </c>
+      <c r="K172">
+        <v>3.83</v>
+      </c>
+      <c r="L172">
+        <v>184440</v>
+      </c>
+      <c r="M172">
+        <v>22050</v>
+      </c>
+      <c r="N172">
+        <v>352.88</v>
+      </c>
+      <c r="O172">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>101</v>
+      </c>
+      <c r="C173" t="s">
+        <v>136</v>
+      </c>
+      <c r="D173" t="s">
+        <v>138</v>
+      </c>
+      <c r="E173" t="s">
+        <v>140</v>
+      </c>
+      <c r="F173">
+        <v>93</v>
+      </c>
+      <c r="G173">
+        <v>17</v>
+      </c>
+      <c r="H173">
+        <v>4295.78</v>
+      </c>
+      <c r="I173">
+        <v>7.288</v>
+      </c>
+      <c r="J173">
+        <v>11583.94</v>
+      </c>
+      <c r="K173">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="L173">
+        <v>117072</v>
+      </c>
+      <c r="M173">
+        <v>44100</v>
+      </c>
+      <c r="N173">
+        <v>128</v>
+      </c>
+      <c r="O173">
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>101</v>
+      </c>
+      <c r="C174" t="s">
+        <v>137</v>
+      </c>
+      <c r="D174" t="s">
+        <v>139</v>
+      </c>
+      <c r="E174" t="s">
+        <v>141</v>
+      </c>
+      <c r="F174">
+        <v>93</v>
+      </c>
+      <c r="G174">
+        <v>17</v>
+      </c>
+      <c r="H174">
+        <v>6615.28</v>
+      </c>
+      <c r="I174">
+        <v>7.509</v>
+      </c>
+      <c r="J174">
+        <v>14124.62</v>
+      </c>
+      <c r="K174">
+        <v>6.58</v>
+      </c>
+      <c r="L174">
+        <v>331206</v>
+      </c>
+      <c r="M174">
+        <v>22050</v>
+      </c>
+      <c r="N174">
+        <v>352.85</v>
+      </c>
+      <c r="O174">
+        <v>0.1395</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>102</v>
+      </c>
+      <c r="C175" t="s">
+        <v>136</v>
+      </c>
+      <c r="D175" t="s">
+        <v>138</v>
+      </c>
+      <c r="E175" t="s">
+        <v>140</v>
+      </c>
+      <c r="F175">
+        <v>31</v>
+      </c>
+      <c r="G175">
+        <v>7</v>
+      </c>
+      <c r="H175">
+        <v>1281.45</v>
+      </c>
+      <c r="I175">
+        <v>2.403</v>
+      </c>
+      <c r="J175">
+        <v>3684.71</v>
+      </c>
+      <c r="K175">
+        <v>8.41</v>
+      </c>
+      <c r="L175">
+        <v>38914</v>
+      </c>
+      <c r="M175">
+        <v>44100</v>
+      </c>
+      <c r="N175">
+        <v>128</v>
+      </c>
+      <c r="O175">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>102</v>
+      </c>
+      <c r="C176" t="s">
+        <v>137</v>
+      </c>
+      <c r="D176" t="s">
+        <v>139</v>
+      </c>
+      <c r="E176" t="s">
+        <v>141</v>
+      </c>
+      <c r="F176">
+        <v>31</v>
+      </c>
+      <c r="G176">
+        <v>7</v>
+      </c>
+      <c r="H176">
+        <v>2247.18</v>
+      </c>
+      <c r="I176">
+        <v>2.731</v>
+      </c>
+      <c r="J176">
+        <v>4977.84</v>
+      </c>
+      <c r="K176">
+        <v>6.23</v>
+      </c>
+      <c r="L176">
+        <v>120466</v>
+      </c>
+      <c r="M176">
+        <v>22050</v>
+      </c>
+      <c r="N176">
+        <v>352.93</v>
+      </c>
+      <c r="O176">
+        <v>0.0465</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>103</v>
+      </c>
+      <c r="C177" t="s">
+        <v>136</v>
+      </c>
+      <c r="D177" t="s">
+        <v>138</v>
+      </c>
+      <c r="E177" t="s">
+        <v>140</v>
+      </c>
+      <c r="F177">
+        <v>40</v>
+      </c>
+      <c r="G177">
+        <v>8</v>
+      </c>
+      <c r="H177">
+        <v>1963.61</v>
+      </c>
+      <c r="I177">
+        <v>2.743</v>
+      </c>
+      <c r="J177">
+        <v>4706.46</v>
+      </c>
+      <c r="K177">
+        <v>8.5</v>
+      </c>
+      <c r="L177">
+        <v>44347</v>
+      </c>
+      <c r="M177">
+        <v>44100</v>
+      </c>
+      <c r="N177">
+        <v>128</v>
+      </c>
+      <c r="O177">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>103</v>
+      </c>
+      <c r="C178" t="s">
+        <v>137</v>
+      </c>
+      <c r="D178" t="s">
+        <v>139</v>
+      </c>
+      <c r="E178" t="s">
+        <v>141</v>
+      </c>
+      <c r="F178">
+        <v>40</v>
+      </c>
+      <c r="G178">
+        <v>8</v>
+      </c>
+      <c r="H178">
+        <v>4027.62</v>
+      </c>
+      <c r="I178">
+        <v>3.413</v>
+      </c>
+      <c r="J178">
+        <v>7440.96</v>
+      </c>
+      <c r="K178">
+        <v>5.38</v>
+      </c>
+      <c r="L178">
+        <v>150572</v>
+      </c>
+      <c r="M178">
+        <v>22050</v>
+      </c>
+      <c r="N178">
+        <v>352.9</v>
+      </c>
+      <c r="O178">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>104</v>
+      </c>
+      <c r="C179" t="s">
+        <v>136</v>
+      </c>
+      <c r="D179" t="s">
+        <v>138</v>
+      </c>
+      <c r="E179" t="s">
+        <v>140</v>
+      </c>
+      <c r="F179">
+        <v>36</v>
+      </c>
+      <c r="G179">
+        <v>8</v>
+      </c>
+      <c r="H179">
+        <v>1368.48</v>
+      </c>
+      <c r="I179">
+        <v>2.873</v>
+      </c>
+      <c r="J179">
+        <v>4241.95</v>
+      </c>
+      <c r="K179">
+        <v>8.49</v>
+      </c>
+      <c r="L179">
+        <v>46437</v>
+      </c>
+      <c r="M179">
+        <v>44100</v>
+      </c>
+      <c r="N179">
+        <v>128</v>
+      </c>
+      <c r="O179">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>104</v>
+      </c>
+      <c r="C180" t="s">
+        <v>137</v>
+      </c>
+      <c r="D180" t="s">
+        <v>139</v>
+      </c>
+      <c r="E180" t="s">
+        <v>141</v>
+      </c>
+      <c r="F180">
+        <v>36</v>
+      </c>
+      <c r="G180">
+        <v>8</v>
+      </c>
+      <c r="H180">
+        <v>4948.5</v>
+      </c>
+      <c r="I180">
+        <v>3.413</v>
+      </c>
+      <c r="J180">
+        <v>8361.84</v>
+      </c>
+      <c r="K180">
+        <v>4.31</v>
+      </c>
+      <c r="L180">
+        <v>150572</v>
+      </c>
+      <c r="M180">
+        <v>22050</v>
+      </c>
+      <c r="N180">
+        <v>352.9</v>
+      </c>
+      <c r="O180">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>105</v>
+      </c>
+      <c r="C181" t="s">
+        <v>136</v>
+      </c>
+      <c r="D181" t="s">
+        <v>138</v>
+      </c>
+      <c r="E181" t="s">
+        <v>140</v>
+      </c>
+      <c r="F181">
+        <v>22</v>
+      </c>
+      <c r="G181">
+        <v>5</v>
+      </c>
+      <c r="H181">
+        <v>1383.85</v>
+      </c>
+      <c r="I181">
+        <v>1.933</v>
+      </c>
+      <c r="J181">
+        <v>3316.91</v>
+      </c>
+      <c r="K181">
+        <v>6.63</v>
+      </c>
+      <c r="L181">
+        <v>31391</v>
+      </c>
+      <c r="M181">
+        <v>44100</v>
+      </c>
+      <c r="N181">
+        <v>128</v>
+      </c>
+      <c r="O181">
+        <v>0.08799999999999999</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>105</v>
+      </c>
+      <c r="C182" t="s">
+        <v>137</v>
+      </c>
+      <c r="D182" t="s">
+        <v>139</v>
+      </c>
+      <c r="E182" t="s">
+        <v>141</v>
+      </c>
+      <c r="F182">
+        <v>22</v>
+      </c>
+      <c r="G182">
+        <v>5</v>
+      </c>
+      <c r="H182">
+        <v>1899.3</v>
+      </c>
+      <c r="I182">
+        <v>2.133</v>
+      </c>
+      <c r="J182">
+        <v>4032.63</v>
+      </c>
+      <c r="K182">
+        <v>5.46</v>
+      </c>
+      <c r="L182">
+        <v>94124</v>
+      </c>
+      <c r="M182">
+        <v>22050</v>
+      </c>
+      <c r="N182">
+        <v>352.96</v>
+      </c>
+      <c r="O182">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>106</v>
+      </c>
+      <c r="C183" t="s">
+        <v>136</v>
+      </c>
+      <c r="D183" t="s">
+        <v>138</v>
+      </c>
+      <c r="E183" t="s">
+        <v>140</v>
+      </c>
+      <c r="F183">
+        <v>94</v>
+      </c>
+      <c r="G183">
+        <v>20</v>
+      </c>
+      <c r="H183">
+        <v>1700.33</v>
+      </c>
+      <c r="I183">
+        <v>7.236</v>
+      </c>
+      <c r="J183">
+        <v>8936.25</v>
+      </c>
+      <c r="K183">
+        <v>10.52</v>
+      </c>
+      <c r="L183">
+        <v>116236</v>
+      </c>
+      <c r="M183">
+        <v>44100</v>
+      </c>
+      <c r="N183">
+        <v>128</v>
+      </c>
+      <c r="O183">
+        <v>0.376</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>106</v>
+      </c>
+      <c r="C184" t="s">
+        <v>137</v>
+      </c>
+      <c r="D184" t="s">
+        <v>139</v>
+      </c>
+      <c r="E184" t="s">
+        <v>141</v>
+      </c>
+      <c r="F184">
+        <v>94</v>
+      </c>
+      <c r="G184">
+        <v>20</v>
+      </c>
+      <c r="H184">
+        <v>4504.06</v>
+      </c>
+      <c r="I184">
+        <v>8.448</v>
+      </c>
+      <c r="J184">
+        <v>12952.04</v>
+      </c>
+      <c r="K184">
+        <v>7.26</v>
+      </c>
+      <c r="L184">
+        <v>372600</v>
+      </c>
+      <c r="M184">
+        <v>22050</v>
+      </c>
+      <c r="N184">
+        <v>352.84</v>
+      </c>
+      <c r="O184">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>107</v>
+      </c>
+      <c r="C185" t="s">
+        <v>136</v>
+      </c>
+      <c r="D185" t="s">
+        <v>138</v>
+      </c>
+      <c r="E185" t="s">
+        <v>140</v>
+      </c>
+      <c r="F185">
+        <v>44</v>
+      </c>
+      <c r="G185">
+        <v>10</v>
+      </c>
+      <c r="H185">
+        <v>1346.15</v>
+      </c>
+      <c r="I185">
+        <v>3.527</v>
+      </c>
+      <c r="J185">
+        <v>4872.68</v>
+      </c>
+      <c r="K185">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="L185">
+        <v>56886</v>
+      </c>
+      <c r="M185">
+        <v>44100</v>
+      </c>
+      <c r="N185">
+        <v>128</v>
+      </c>
+      <c r="O185">
+        <v>0.176</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>107</v>
+      </c>
+      <c r="C186" t="s">
+        <v>137</v>
+      </c>
+      <c r="D186" t="s">
+        <v>139</v>
+      </c>
+      <c r="E186" t="s">
+        <v>141</v>
+      </c>
+      <c r="F186">
+        <v>44</v>
+      </c>
+      <c r="G186">
+        <v>10</v>
+      </c>
+      <c r="H186">
+        <v>2756.84</v>
+      </c>
+      <c r="I186">
+        <v>3.669</v>
+      </c>
+      <c r="J186">
+        <v>6426.19</v>
+      </c>
+      <c r="K186">
+        <v>6.85</v>
+      </c>
+      <c r="L186">
+        <v>161862</v>
+      </c>
+      <c r="M186">
+        <v>22050</v>
+      </c>
+      <c r="N186">
+        <v>352.9</v>
+      </c>
+      <c r="O186">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>108</v>
+      </c>
+      <c r="C187" t="s">
+        <v>136</v>
+      </c>
+      <c r="D187" t="s">
+        <v>138</v>
+      </c>
+      <c r="E187" t="s">
+        <v>140</v>
+      </c>
+      <c r="F187">
+        <v>40</v>
+      </c>
+      <c r="G187">
+        <v>7</v>
+      </c>
+      <c r="H187">
+        <v>1232.54</v>
+      </c>
+      <c r="I187">
+        <v>2.22</v>
+      </c>
+      <c r="J187">
+        <v>3452.95</v>
+      </c>
+      <c r="K187">
+        <v>11.58</v>
+      </c>
+      <c r="L187">
+        <v>35988</v>
+      </c>
+      <c r="M187">
+        <v>44100</v>
+      </c>
+      <c r="N187">
+        <v>128</v>
+      </c>
+      <c r="O187">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>108</v>
+      </c>
+      <c r="C188" t="s">
+        <v>137</v>
+      </c>
+      <c r="D188" t="s">
+        <v>139</v>
+      </c>
+      <c r="E188" t="s">
+        <v>141</v>
+      </c>
+      <c r="F188">
+        <v>40</v>
+      </c>
+      <c r="G188">
+        <v>7</v>
+      </c>
+      <c r="H188">
+        <v>1761.81</v>
+      </c>
+      <c r="I188">
+        <v>2.901</v>
+      </c>
+      <c r="J188">
+        <v>4663.12</v>
+      </c>
+      <c r="K188">
+        <v>8.58</v>
+      </c>
+      <c r="L188">
+        <v>127992</v>
+      </c>
+      <c r="M188">
+        <v>22050</v>
+      </c>
+      <c r="N188">
+        <v>352.92</v>
+      </c>
+      <c r="O188">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>109</v>
+      </c>
+      <c r="C189" t="s">
+        <v>136</v>
+      </c>
+      <c r="D189" t="s">
+        <v>138</v>
+      </c>
+      <c r="E189" t="s">
+        <v>140</v>
+      </c>
+      <c r="F189">
+        <v>46</v>
+      </c>
+      <c r="G189">
+        <v>11</v>
+      </c>
+      <c r="H189">
+        <v>1340.09</v>
+      </c>
+      <c r="I189">
+        <v>3.056</v>
+      </c>
+      <c r="J189">
+        <v>4396.42</v>
+      </c>
+      <c r="K189">
+        <v>10.46</v>
+      </c>
+      <c r="L189">
+        <v>49363</v>
+      </c>
+      <c r="M189">
+        <v>44100</v>
+      </c>
+      <c r="N189">
+        <v>128</v>
+      </c>
+      <c r="O189">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>109</v>
+      </c>
+      <c r="C190" t="s">
+        <v>137</v>
+      </c>
+      <c r="D190" t="s">
+        <v>139</v>
+      </c>
+      <c r="E190" t="s">
+        <v>141</v>
+      </c>
+      <c r="F190">
+        <v>46</v>
+      </c>
+      <c r="G190">
+        <v>11</v>
+      </c>
+      <c r="H190">
+        <v>2500.74</v>
+      </c>
+      <c r="I190">
+        <v>4.181</v>
+      </c>
+      <c r="J190">
+        <v>6682.06</v>
+      </c>
+      <c r="K190">
+        <v>6.88</v>
+      </c>
+      <c r="L190">
+        <v>184440</v>
+      </c>
+      <c r="M190">
+        <v>22050</v>
+      </c>
+      <c r="N190">
+        <v>352.88</v>
+      </c>
+      <c r="O190">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>110</v>
+      </c>
+      <c r="C191" t="s">
+        <v>136</v>
+      </c>
+      <c r="D191" t="s">
+        <v>138</v>
+      </c>
+      <c r="E191" t="s">
+        <v>140</v>
+      </c>
+      <c r="F191">
+        <v>52</v>
+      </c>
+      <c r="G191">
+        <v>11</v>
+      </c>
+      <c r="H191">
+        <v>2351.79</v>
+      </c>
+      <c r="I191">
+        <v>4.023</v>
+      </c>
+      <c r="J191">
+        <v>6374.65</v>
+      </c>
+      <c r="K191">
+        <v>8.16</v>
+      </c>
+      <c r="L191">
+        <v>64827</v>
+      </c>
+      <c r="M191">
+        <v>44100</v>
+      </c>
+      <c r="N191">
+        <v>128</v>
+      </c>
+      <c r="O191">
+        <v>0.208</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>110</v>
+      </c>
+      <c r="C192" t="s">
+        <v>137</v>
+      </c>
+      <c r="D192" t="s">
+        <v>139</v>
+      </c>
+      <c r="E192" t="s">
+        <v>141</v>
+      </c>
+      <c r="F192">
+        <v>52</v>
+      </c>
+      <c r="G192">
+        <v>11</v>
+      </c>
+      <c r="H192">
+        <v>6433.88</v>
+      </c>
+      <c r="I192">
+        <v>6.059</v>
+      </c>
+      <c r="J192">
+        <v>12492.56</v>
+      </c>
+      <c r="K192">
+        <v>4.16</v>
+      </c>
+      <c r="L192">
+        <v>267232</v>
+      </c>
+      <c r="M192">
+        <v>22050</v>
+      </c>
+      <c r="N192">
+        <v>352.86</v>
+      </c>
+      <c r="O192">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>111</v>
+      </c>
+      <c r="C193" t="s">
+        <v>136</v>
+      </c>
+      <c r="D193" t="s">
+        <v>138</v>
+      </c>
+      <c r="E193" t="s">
+        <v>140</v>
+      </c>
+      <c r="F193">
+        <v>41</v>
+      </c>
+      <c r="G193">
+        <v>9</v>
+      </c>
+      <c r="H193">
+        <v>1726.42</v>
+      </c>
+      <c r="I193">
+        <v>3.187</v>
+      </c>
+      <c r="J193">
+        <v>4913.36</v>
+      </c>
+      <c r="K193">
+        <v>8.34</v>
+      </c>
+      <c r="L193">
+        <v>51453</v>
+      </c>
+      <c r="M193">
+        <v>44100</v>
+      </c>
+      <c r="N193">
+        <v>128</v>
+      </c>
+      <c r="O193">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>111</v>
+      </c>
+      <c r="C194" t="s">
+        <v>137</v>
+      </c>
+      <c r="D194" t="s">
+        <v>139</v>
+      </c>
+      <c r="E194" t="s">
+        <v>141</v>
+      </c>
+      <c r="F194">
+        <v>41</v>
+      </c>
+      <c r="G194">
+        <v>9</v>
+      </c>
+      <c r="H194">
+        <v>2380.96</v>
+      </c>
+      <c r="I194">
+        <v>3.328</v>
+      </c>
+      <c r="J194">
+        <v>5708.94</v>
+      </c>
+      <c r="K194">
+        <v>7.18</v>
+      </c>
+      <c r="L194">
+        <v>146808</v>
+      </c>
+      <c r="M194">
+        <v>22050</v>
+      </c>
+      <c r="N194">
+        <v>352.91</v>
+      </c>
+      <c r="O194">
+        <v>0.0615</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>112</v>
+      </c>
+      <c r="C195" t="s">
+        <v>136</v>
+      </c>
+      <c r="D195" t="s">
+        <v>138</v>
+      </c>
+      <c r="E195" t="s">
+        <v>140</v>
+      </c>
+      <c r="F195">
+        <v>42</v>
+      </c>
+      <c r="G195">
+        <v>10</v>
+      </c>
+      <c r="H195">
+        <v>1626.29</v>
+      </c>
+      <c r="I195">
+        <v>2.691</v>
+      </c>
+      <c r="J195">
+        <v>4316.9</v>
+      </c>
+      <c r="K195">
+        <v>9.73</v>
+      </c>
+      <c r="L195">
+        <v>43511</v>
+      </c>
+      <c r="M195">
+        <v>44100</v>
+      </c>
+      <c r="N195">
+        <v>128</v>
+      </c>
+      <c r="O195">
+        <v>0.168</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>112</v>
+      </c>
+      <c r="C196" t="s">
+        <v>137</v>
+      </c>
+      <c r="D196" t="s">
+        <v>139</v>
+      </c>
+      <c r="E196" t="s">
+        <v>141</v>
+      </c>
+      <c r="F196">
+        <v>42</v>
+      </c>
+      <c r="G196">
+        <v>10</v>
+      </c>
+      <c r="H196">
+        <v>2406.42</v>
+      </c>
+      <c r="I196">
+        <v>3.413</v>
+      </c>
+      <c r="J196">
+        <v>5819.75</v>
+      </c>
+      <c r="K196">
+        <v>7.22</v>
+      </c>
+      <c r="L196">
+        <v>150572</v>
+      </c>
+      <c r="M196">
+        <v>22050</v>
+      </c>
+      <c r="N196">
+        <v>352.9</v>
+      </c>
+      <c r="O196">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>113</v>
+      </c>
+      <c r="C197" t="s">
+        <v>136</v>
+      </c>
+      <c r="D197" t="s">
+        <v>138</v>
+      </c>
+      <c r="E197" t="s">
+        <v>140</v>
+      </c>
+      <c r="F197">
+        <v>49</v>
+      </c>
+      <c r="G197">
+        <v>11</v>
+      </c>
+      <c r="H197">
+        <v>1702.73</v>
+      </c>
+      <c r="I197">
+        <v>3.187</v>
+      </c>
+      <c r="J197">
+        <v>4889.67</v>
+      </c>
+      <c r="K197">
+        <v>10.02</v>
+      </c>
+      <c r="L197">
+        <v>51453</v>
+      </c>
+      <c r="M197">
+        <v>44100</v>
+      </c>
+      <c r="N197">
+        <v>128</v>
+      </c>
+      <c r="O197">
+        <v>0.196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>113</v>
+      </c>
+      <c r="C198" t="s">
+        <v>137</v>
+      </c>
+      <c r="D198" t="s">
+        <v>139</v>
+      </c>
+      <c r="E198" t="s">
+        <v>141</v>
+      </c>
+      <c r="F198">
+        <v>49</v>
+      </c>
+      <c r="G198">
+        <v>11</v>
+      </c>
+      <c r="H198">
+        <v>2203.45</v>
+      </c>
+      <c r="I198">
+        <v>2.987</v>
+      </c>
+      <c r="J198">
+        <v>5190.11</v>
+      </c>
+      <c r="K198">
+        <v>9.44</v>
+      </c>
+      <c r="L198">
+        <v>131756</v>
+      </c>
+      <c r="M198">
+        <v>22050</v>
+      </c>
+      <c r="N198">
+        <v>352.92</v>
+      </c>
+      <c r="O198">
+        <v>0.0735</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>114</v>
+      </c>
+      <c r="C199" t="s">
+        <v>136</v>
+      </c>
+      <c r="D199" t="s">
+        <v>138</v>
+      </c>
+      <c r="E199" t="s">
+        <v>140</v>
+      </c>
+      <c r="F199">
+        <v>49</v>
+      </c>
+      <c r="G199">
+        <v>10</v>
+      </c>
+      <c r="H199">
+        <v>3026.93</v>
+      </c>
+      <c r="I199">
+        <v>4.493</v>
+      </c>
+      <c r="J199">
+        <v>7519.99</v>
+      </c>
+      <c r="K199">
+        <v>6.52</v>
+      </c>
+      <c r="L199">
+        <v>72351</v>
+      </c>
+      <c r="M199">
+        <v>44100</v>
+      </c>
+      <c r="N199">
+        <v>128</v>
+      </c>
+      <c r="O199">
+        <v>0.196</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>114</v>
+      </c>
+      <c r="C200" t="s">
+        <v>137</v>
+      </c>
+      <c r="D200" t="s">
+        <v>139</v>
+      </c>
+      <c r="E200" t="s">
+        <v>141</v>
+      </c>
+      <c r="F200">
+        <v>49</v>
+      </c>
+      <c r="G200">
+        <v>10</v>
+      </c>
+      <c r="H200">
+        <v>2903.64</v>
+      </c>
+      <c r="I200">
+        <v>5.12</v>
+      </c>
+      <c r="J200">
+        <v>8023.64</v>
+      </c>
+      <c r="K200">
+        <v>6.11</v>
+      </c>
+      <c r="L200">
+        <v>225836</v>
+      </c>
+      <c r="M200">
+        <v>22050</v>
+      </c>
+      <c r="N200">
+        <v>352.87</v>
+      </c>
+      <c r="O200">
+        <v>0.0735</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>115</v>
+      </c>
+      <c r="C201" t="s">
+        <v>136</v>
+      </c>
+      <c r="D201" t="s">
+        <v>138</v>
+      </c>
+      <c r="E201" t="s">
+        <v>140</v>
+      </c>
+      <c r="F201">
+        <v>72</v>
+      </c>
+      <c r="G201">
+        <v>14</v>
+      </c>
+      <c r="H201">
+        <v>1969.46</v>
+      </c>
+      <c r="I201">
+        <v>5.799</v>
+      </c>
+      <c r="J201">
+        <v>7768.65</v>
+      </c>
+      <c r="K201">
+        <v>9.27</v>
+      </c>
+      <c r="L201">
+        <v>93248</v>
+      </c>
+      <c r="M201">
+        <v>44100</v>
+      </c>
+      <c r="N201">
+        <v>128</v>
+      </c>
+      <c r="O201">
+        <v>0.288</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>115</v>
+      </c>
+      <c r="C202" t="s">
+        <v>137</v>
+      </c>
+      <c r="D202" t="s">
+        <v>139</v>
+      </c>
+      <c r="E202" t="s">
+        <v>141</v>
+      </c>
+      <c r="F202">
+        <v>72</v>
+      </c>
+      <c r="G202">
+        <v>14</v>
+      </c>
+      <c r="H202">
+        <v>2977.95</v>
+      </c>
+      <c r="I202">
+        <v>5.376</v>
+      </c>
+      <c r="J202">
+        <v>8353.959999999999</v>
+      </c>
+      <c r="K202">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="L202">
+        <v>237126</v>
+      </c>
+      <c r="M202">
+        <v>22050</v>
+      </c>
+      <c r="N202">
+        <v>352.87</v>
+      </c>
+      <c r="O202">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>116</v>
+      </c>
+      <c r="C203" t="s">
+        <v>136</v>
+      </c>
+      <c r="D203" t="s">
+        <v>138</v>
+      </c>
+      <c r="E203" t="s">
+        <v>140</v>
+      </c>
+      <c r="F203">
+        <v>21</v>
+      </c>
+      <c r="G203">
+        <v>5</v>
+      </c>
+      <c r="H203">
+        <v>1268.74</v>
+      </c>
+      <c r="I203">
+        <v>1.855</v>
+      </c>
+      <c r="J203">
+        <v>3123.43</v>
+      </c>
+      <c r="K203">
+        <v>6.72</v>
+      </c>
+      <c r="L203">
+        <v>30137</v>
+      </c>
+      <c r="M203">
+        <v>44100</v>
+      </c>
+      <c r="N203">
+        <v>128</v>
+      </c>
+      <c r="O203">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>116</v>
+      </c>
+      <c r="C204" t="s">
+        <v>137</v>
+      </c>
+      <c r="D204" t="s">
+        <v>139</v>
+      </c>
+      <c r="E204" t="s">
+        <v>141</v>
+      </c>
+      <c r="F204">
+        <v>21</v>
+      </c>
+      <c r="G204">
+        <v>5</v>
+      </c>
+      <c r="H204">
+        <v>3908.29</v>
+      </c>
+      <c r="I204">
+        <v>2.56</v>
+      </c>
+      <c r="J204">
+        <v>6468.29</v>
+      </c>
+      <c r="K204">
+        <v>3.25</v>
+      </c>
+      <c r="L204">
+        <v>112940</v>
+      </c>
+      <c r="M204">
+        <v>22050</v>
+      </c>
+      <c r="N204">
+        <v>352.94</v>
+      </c>
+      <c r="O204">
+        <v>0.0315</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>117</v>
+      </c>
+      <c r="C205" t="s">
+        <v>136</v>
+      </c>
+      <c r="D205" t="s">
+        <v>138</v>
+      </c>
+      <c r="E205" t="s">
+        <v>140</v>
+      </c>
+      <c r="F205">
+        <v>48</v>
+      </c>
+      <c r="G205">
+        <v>9</v>
+      </c>
+      <c r="H205">
+        <v>7026.48</v>
+      </c>
+      <c r="I205">
+        <v>3.474</v>
+      </c>
+      <c r="J205">
+        <v>10500.76</v>
+      </c>
+      <c r="K205">
+        <v>4.57</v>
+      </c>
+      <c r="L205">
+        <v>56050</v>
+      </c>
+      <c r="M205">
+        <v>44100</v>
+      </c>
+      <c r="N205">
+        <v>128</v>
+      </c>
+      <c r="O205">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>117</v>
+      </c>
+      <c r="C206" t="s">
+        <v>137</v>
+      </c>
+      <c r="D206" t="s">
+        <v>139</v>
+      </c>
+      <c r="E206" t="s">
+        <v>141</v>
+      </c>
+      <c r="F206">
+        <v>48</v>
+      </c>
+      <c r="G206">
+        <v>9</v>
+      </c>
+      <c r="H206">
+        <v>4141.7</v>
+      </c>
+      <c r="I206">
+        <v>3.669</v>
+      </c>
+      <c r="J206">
+        <v>7811.04</v>
+      </c>
+      <c r="K206">
+        <v>6.15</v>
+      </c>
+      <c r="L206">
+        <v>161862</v>
+      </c>
+      <c r="M206">
+        <v>22050</v>
+      </c>
+      <c r="N206">
+        <v>352.9</v>
+      </c>
+      <c r="O206">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>118</v>
+      </c>
+      <c r="C207" t="s">
+        <v>136</v>
+      </c>
+      <c r="D207" t="s">
+        <v>138</v>
+      </c>
+      <c r="E207" t="s">
+        <v>140</v>
+      </c>
+      <c r="F207">
+        <v>56</v>
+      </c>
+      <c r="G207">
+        <v>10</v>
+      </c>
+      <c r="H207">
+        <v>1408.89</v>
+      </c>
+      <c r="I207">
+        <v>3.422</v>
+      </c>
+      <c r="J207">
+        <v>4830.93</v>
+      </c>
+      <c r="K207">
+        <v>11.59</v>
+      </c>
+      <c r="L207">
+        <v>55214</v>
+      </c>
+      <c r="M207">
+        <v>44100</v>
+      </c>
+      <c r="N207">
+        <v>128</v>
+      </c>
+      <c r="O207">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>118</v>
+      </c>
+      <c r="C208" t="s">
+        <v>137</v>
+      </c>
+      <c r="D208" t="s">
+        <v>139</v>
+      </c>
+      <c r="E208" t="s">
+        <v>141</v>
+      </c>
+      <c r="F208">
+        <v>56</v>
+      </c>
+      <c r="G208">
+        <v>10</v>
+      </c>
+      <c r="H208">
+        <v>3394.2</v>
+      </c>
+      <c r="I208">
+        <v>4.352</v>
+      </c>
+      <c r="J208">
+        <v>7746.22</v>
+      </c>
+      <c r="K208">
+        <v>7.23</v>
+      </c>
+      <c r="L208">
+        <v>191968</v>
+      </c>
+      <c r="M208">
+        <v>22050</v>
+      </c>
+      <c r="N208">
+        <v>352.88</v>
+      </c>
+      <c r="O208">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>119</v>
+      </c>
+      <c r="C209" t="s">
+        <v>136</v>
+      </c>
+      <c r="D209" t="s">
+        <v>138</v>
+      </c>
+      <c r="E209" t="s">
+        <v>140</v>
+      </c>
+      <c r="F209">
+        <v>66</v>
+      </c>
+      <c r="G209">
+        <v>13</v>
+      </c>
+      <c r="H209">
+        <v>3013.71</v>
+      </c>
+      <c r="I209">
+        <v>5.198</v>
+      </c>
+      <c r="J209">
+        <v>8212.07</v>
+      </c>
+      <c r="K209">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="L209">
+        <v>83635</v>
+      </c>
+      <c r="M209">
+        <v>44100</v>
+      </c>
+      <c r="N209">
+        <v>128</v>
+      </c>
+      <c r="O209">
+        <v>0.264</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>119</v>
+      </c>
+      <c r="C210" t="s">
+        <v>137</v>
+      </c>
+      <c r="D210" t="s">
+        <v>139</v>
+      </c>
+      <c r="E210" t="s">
+        <v>141</v>
+      </c>
+      <c r="F210">
+        <v>66</v>
+      </c>
+      <c r="G210">
+        <v>13</v>
+      </c>
+      <c r="H210">
+        <v>3316.76</v>
+      </c>
+      <c r="I210">
+        <v>4.864</v>
+      </c>
+      <c r="J210">
+        <v>8180.75</v>
+      </c>
+      <c r="K210">
+        <v>8.07</v>
+      </c>
+      <c r="L210">
+        <v>214546</v>
+      </c>
+      <c r="M210">
+        <v>22050</v>
+      </c>
+      <c r="N210">
+        <v>352.87</v>
+      </c>
+      <c r="O210">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>120</v>
+      </c>
+      <c r="C211" t="s">
+        <v>136</v>
+      </c>
+      <c r="D211" t="s">
+        <v>138</v>
+      </c>
+      <c r="E211" t="s">
+        <v>140</v>
+      </c>
+      <c r="F211">
+        <v>41</v>
+      </c>
+      <c r="G211">
+        <v>8</v>
+      </c>
+      <c r="H211">
+        <v>1564.62</v>
+      </c>
+      <c r="I211">
+        <v>3.527</v>
+      </c>
+      <c r="J211">
+        <v>5091.15</v>
+      </c>
+      <c r="K211">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="L211">
+        <v>56886</v>
+      </c>
+      <c r="M211">
+        <v>44100</v>
+      </c>
+      <c r="N211">
+        <v>128</v>
+      </c>
+      <c r="O211">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>120</v>
+      </c>
+      <c r="C212" t="s">
+        <v>137</v>
+      </c>
+      <c r="D212" t="s">
+        <v>139</v>
+      </c>
+      <c r="E212" t="s">
+        <v>141</v>
+      </c>
+      <c r="F212">
+        <v>41</v>
+      </c>
+      <c r="G212">
+        <v>8</v>
+      </c>
+      <c r="H212">
+        <v>1914.36</v>
+      </c>
+      <c r="I212">
+        <v>3.243</v>
+      </c>
+      <c r="J212">
+        <v>5157.03</v>
+      </c>
+      <c r="K212">
+        <v>7.95</v>
+      </c>
+      <c r="L212">
+        <v>143046</v>
+      </c>
+      <c r="M212">
+        <v>22050</v>
+      </c>
+      <c r="N212">
+        <v>352.91</v>
+      </c>
+      <c r="O212">
+        <v>0.0615</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>121</v>
+      </c>
+      <c r="C213" t="s">
+        <v>136</v>
+      </c>
+      <c r="D213" t="s">
+        <v>138</v>
+      </c>
+      <c r="E213" t="s">
+        <v>140</v>
+      </c>
+      <c r="F213">
+        <v>56</v>
+      </c>
+      <c r="G213">
+        <v>13</v>
+      </c>
+      <c r="H213">
+        <v>1355.78</v>
+      </c>
+      <c r="I213">
+        <v>3.474</v>
+      </c>
+      <c r="J213">
+        <v>4830.06</v>
+      </c>
+      <c r="K213">
+        <v>11.59</v>
+      </c>
+      <c r="L213">
+        <v>56050</v>
+      </c>
+      <c r="M213">
+        <v>44100</v>
+      </c>
+      <c r="N213">
+        <v>128</v>
+      </c>
+      <c r="O213">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>121</v>
+      </c>
+      <c r="C214" t="s">
+        <v>137</v>
+      </c>
+      <c r="D214" t="s">
+        <v>139</v>
+      </c>
+      <c r="E214" t="s">
+        <v>141</v>
+      </c>
+      <c r="F214">
+        <v>56</v>
+      </c>
+      <c r="G214">
+        <v>13</v>
+      </c>
+      <c r="H214">
+        <v>2326.46</v>
+      </c>
+      <c r="I214">
+        <v>3.584</v>
+      </c>
+      <c r="J214">
+        <v>5910.45</v>
+      </c>
+      <c r="K214">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="L214">
+        <v>158098</v>
+      </c>
+      <c r="M214">
+        <v>22050</v>
+      </c>
+      <c r="N214">
+        <v>352.9</v>
+      </c>
+      <c r="O214">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>122</v>
+      </c>
+      <c r="C215" t="s">
+        <v>136</v>
+      </c>
+      <c r="D215" t="s">
+        <v>138</v>
+      </c>
+      <c r="E215" t="s">
+        <v>140</v>
+      </c>
+      <c r="F215">
+        <v>35</v>
+      </c>
+      <c r="G215">
+        <v>8</v>
+      </c>
+      <c r="H215">
+        <v>1335.19</v>
+      </c>
+      <c r="I215">
+        <v>2.534</v>
+      </c>
+      <c r="J215">
+        <v>3869.07</v>
+      </c>
+      <c r="K215">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="L215">
+        <v>41004</v>
+      </c>
+      <c r="M215">
+        <v>44100</v>
+      </c>
+      <c r="N215">
+        <v>128</v>
+      </c>
+      <c r="O215">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>122</v>
+      </c>
+      <c r="C216" t="s">
+        <v>137</v>
+      </c>
+      <c r="D216" t="s">
+        <v>139</v>
+      </c>
+      <c r="E216" t="s">
+        <v>141</v>
+      </c>
+      <c r="F216">
+        <v>35</v>
+      </c>
+      <c r="G216">
+        <v>8</v>
+      </c>
+      <c r="H216">
+        <v>2385.05</v>
+      </c>
+      <c r="I216">
+        <v>3.157</v>
+      </c>
+      <c r="J216">
+        <v>5542.37</v>
+      </c>
+      <c r="K216">
+        <v>6.31</v>
+      </c>
+      <c r="L216">
+        <v>139282</v>
+      </c>
+      <c r="M216">
+        <v>22050</v>
+      </c>
+      <c r="N216">
+        <v>352.91</v>
+      </c>
+      <c r="O216">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>123</v>
+      </c>
+      <c r="C217" t="s">
+        <v>136</v>
+      </c>
+      <c r="D217" t="s">
+        <v>138</v>
+      </c>
+      <c r="E217" t="s">
+        <v>140</v>
+      </c>
+      <c r="F217">
+        <v>29</v>
+      </c>
+      <c r="G217">
+        <v>6</v>
+      </c>
+      <c r="H217">
+        <v>1472.33</v>
+      </c>
+      <c r="I217">
+        <v>1.75</v>
+      </c>
+      <c r="J217">
+        <v>3222.53</v>
+      </c>
+      <c r="K217">
+        <v>9</v>
+      </c>
+      <c r="L217">
+        <v>28465</v>
+      </c>
+      <c r="M217">
+        <v>44100</v>
+      </c>
+      <c r="N217">
+        <v>128</v>
+      </c>
+      <c r="O217">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>123</v>
+      </c>
+      <c r="C218" t="s">
+        <v>137</v>
+      </c>
+      <c r="D218" t="s">
+        <v>139</v>
+      </c>
+      <c r="E218" t="s">
+        <v>141</v>
+      </c>
+      <c r="F218">
+        <v>29</v>
+      </c>
+      <c r="G218">
+        <v>6</v>
+      </c>
+      <c r="H218">
+        <v>2164.55</v>
+      </c>
+      <c r="I218">
+        <v>2.56</v>
+      </c>
+      <c r="J218">
+        <v>4724.55</v>
+      </c>
+      <c r="K218">
+        <v>6.14</v>
+      </c>
+      <c r="L218">
+        <v>112940</v>
+      </c>
+      <c r="M218">
+        <v>22050</v>
+      </c>
+      <c r="N218">
+        <v>352.94</v>
+      </c>
+      <c r="O218">
+        <v>0.0435</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>124</v>
+      </c>
+      <c r="C219" t="s">
+        <v>136</v>
+      </c>
+      <c r="D219" t="s">
+        <v>138</v>
+      </c>
+      <c r="E219" t="s">
+        <v>140</v>
+      </c>
+      <c r="F219">
+        <v>27</v>
+      </c>
+      <c r="G219">
+        <v>7</v>
+      </c>
+      <c r="H219">
+        <v>2330.48</v>
+      </c>
+      <c r="I219">
+        <v>2.508</v>
+      </c>
+      <c r="J219">
+        <v>4838.23</v>
+      </c>
+      <c r="K219">
+        <v>5.58</v>
+      </c>
+      <c r="L219">
+        <v>40586</v>
+      </c>
+      <c r="M219">
+        <v>44100</v>
+      </c>
+      <c r="N219">
+        <v>128</v>
+      </c>
+      <c r="O219">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>124</v>
+      </c>
+      <c r="C220" t="s">
+        <v>137</v>
+      </c>
+      <c r="D220" t="s">
+        <v>139</v>
+      </c>
+      <c r="E220" t="s">
+        <v>141</v>
+      </c>
+      <c r="F220">
+        <v>27</v>
+      </c>
+      <c r="G220">
+        <v>7</v>
+      </c>
+      <c r="H220">
+        <v>1737.23</v>
+      </c>
+      <c r="I220">
+        <v>2.389</v>
+      </c>
+      <c r="J220">
+        <v>4126.57</v>
+      </c>
+      <c r="K220">
+        <v>6.54</v>
+      </c>
+      <c r="L220">
+        <v>105414</v>
+      </c>
+      <c r="M220">
+        <v>22050</v>
+      </c>
+      <c r="N220">
+        <v>352.95</v>
+      </c>
+      <c r="O220">
+        <v>0.0405</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>125</v>
+      </c>
+      <c r="C221" t="s">
+        <v>136</v>
+      </c>
+      <c r="D221" t="s">
+        <v>138</v>
+      </c>
+      <c r="E221" t="s">
+        <v>140</v>
+      </c>
+      <c r="F221">
+        <v>34</v>
+      </c>
+      <c r="G221">
+        <v>8</v>
+      </c>
+      <c r="H221">
+        <v>1773.21</v>
+      </c>
+      <c r="I221">
+        <v>2.847</v>
+      </c>
+      <c r="J221">
+        <v>4620.55</v>
+      </c>
+      <c r="K221">
+        <v>7.36</v>
+      </c>
+      <c r="L221">
+        <v>46019</v>
+      </c>
+      <c r="M221">
+        <v>44100</v>
+      </c>
+      <c r="N221">
+        <v>128</v>
+      </c>
+      <c r="O221">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>125</v>
+      </c>
+      <c r="C222" t="s">
+        <v>137</v>
+      </c>
+      <c r="D222" t="s">
+        <v>139</v>
+      </c>
+      <c r="E222" t="s">
+        <v>141</v>
+      </c>
+      <c r="F222">
+        <v>34</v>
+      </c>
+      <c r="G222">
+        <v>8</v>
+      </c>
+      <c r="H222">
+        <v>1852.92</v>
+      </c>
+      <c r="I222">
+        <v>3.072</v>
+      </c>
+      <c r="J222">
+        <v>4924.94</v>
+      </c>
+      <c r="K222">
+        <v>6.9</v>
+      </c>
+      <c r="L222">
+        <v>135520</v>
+      </c>
+      <c r="M222">
+        <v>22050</v>
+      </c>
+      <c r="N222">
+        <v>352.91</v>
+      </c>
+      <c r="O222">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>126</v>
+      </c>
+      <c r="C223" t="s">
+        <v>136</v>
+      </c>
+      <c r="D223" t="s">
+        <v>138</v>
+      </c>
+      <c r="E223" t="s">
+        <v>140</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223">
+        <v>6</v>
+      </c>
+      <c r="H223">
+        <v>1471.05</v>
+      </c>
+      <c r="I223">
+        <v>2.586</v>
+      </c>
+      <c r="J223">
+        <v>4057.18</v>
+      </c>
+      <c r="K223">
+        <v>6.16</v>
+      </c>
+      <c r="L223">
+        <v>41839</v>
+      </c>
+      <c r="M223">
+        <v>44100</v>
+      </c>
+      <c r="N223">
+        <v>128</v>
+      </c>
+      <c r="O223">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>126</v>
+      </c>
+      <c r="C224" t="s">
+        <v>137</v>
+      </c>
+      <c r="D224" t="s">
+        <v>139</v>
+      </c>
+      <c r="E224" t="s">
+        <v>141</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224">
+        <v>6</v>
+      </c>
+      <c r="H224">
+        <v>1361.25</v>
+      </c>
+      <c r="I224">
+        <v>2.304</v>
+      </c>
+      <c r="J224">
+        <v>3665.24</v>
+      </c>
+      <c r="K224">
+        <v>6.82</v>
+      </c>
+      <c r="L224">
+        <v>101650</v>
+      </c>
+      <c r="M224">
+        <v>22050</v>
+      </c>
+      <c r="N224">
+        <v>352.95</v>
+      </c>
+      <c r="O224">
+        <v>0.0375</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>127</v>
+      </c>
+      <c r="C225" t="s">
+        <v>136</v>
+      </c>
+      <c r="D225" t="s">
+        <v>138</v>
+      </c>
+      <c r="E225" t="s">
+        <v>140</v>
+      </c>
+      <c r="F225">
+        <v>78</v>
+      </c>
+      <c r="G225">
+        <v>16</v>
+      </c>
+      <c r="H225">
+        <v>3003.81</v>
+      </c>
+      <c r="I225">
+        <v>7.236</v>
+      </c>
+      <c r="J225">
+        <v>10239.72</v>
+      </c>
+      <c r="K225">
+        <v>7.62</v>
+      </c>
+      <c r="L225">
+        <v>116236</v>
+      </c>
+      <c r="M225">
+        <v>44100</v>
+      </c>
+      <c r="N225">
+        <v>128</v>
+      </c>
+      <c r="O225">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>127</v>
+      </c>
+      <c r="C226" t="s">
+        <v>137</v>
+      </c>
+      <c r="D226" t="s">
+        <v>139</v>
+      </c>
+      <c r="E226" t="s">
+        <v>141</v>
+      </c>
+      <c r="F226">
+        <v>78</v>
+      </c>
+      <c r="G226">
+        <v>16</v>
+      </c>
+      <c r="H226">
+        <v>4049.79</v>
+      </c>
+      <c r="I226">
+        <v>5.291</v>
+      </c>
+      <c r="J226">
+        <v>9340.450000000001</v>
+      </c>
+      <c r="K226">
+        <v>8.35</v>
+      </c>
+      <c r="L226">
+        <v>233362</v>
+      </c>
+      <c r="M226">
+        <v>22050</v>
+      </c>
+      <c r="N226">
+        <v>352.87</v>
+      </c>
+      <c r="O226">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>128</v>
+      </c>
+      <c r="C227" t="s">
+        <v>136</v>
+      </c>
+      <c r="D227" t="s">
+        <v>138</v>
+      </c>
+      <c r="E227" t="s">
+        <v>140</v>
+      </c>
+      <c r="F227">
+        <v>41</v>
+      </c>
+      <c r="G227">
+        <v>9</v>
+      </c>
+      <c r="H227">
+        <v>2895.52</v>
+      </c>
+      <c r="I227">
+        <v>3.553</v>
+      </c>
+      <c r="J227">
+        <v>6448.17</v>
+      </c>
+      <c r="K227">
+        <v>6.36</v>
+      </c>
+      <c r="L227">
+        <v>57304</v>
+      </c>
+      <c r="M227">
+        <v>44100</v>
+      </c>
+      <c r="N227">
+        <v>128</v>
+      </c>
+      <c r="O227">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>128</v>
+      </c>
+      <c r="C228" t="s">
+        <v>137</v>
+      </c>
+      <c r="D228" t="s">
+        <v>139</v>
+      </c>
+      <c r="E228" t="s">
+        <v>141</v>
+      </c>
+      <c r="F228">
+        <v>41</v>
+      </c>
+      <c r="G228">
+        <v>9</v>
+      </c>
+      <c r="H228">
+        <v>1804.61</v>
+      </c>
+      <c r="I228">
+        <v>3.072</v>
+      </c>
+      <c r="J228">
+        <v>4876.62</v>
+      </c>
+      <c r="K228">
+        <v>8.41</v>
+      </c>
+      <c r="L228">
+        <v>135520</v>
+      </c>
+      <c r="M228">
+        <v>22050</v>
+      </c>
+      <c r="N228">
+        <v>352.91</v>
+      </c>
+      <c r="O228">
+        <v>0.0615</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>129</v>
+      </c>
+      <c r="C229" t="s">
+        <v>136</v>
+      </c>
+      <c r="D229" t="s">
+        <v>138</v>
+      </c>
+      <c r="E229" t="s">
+        <v>140</v>
+      </c>
+      <c r="F229">
+        <v>65</v>
+      </c>
+      <c r="G229">
+        <v>13</v>
+      </c>
+      <c r="H229">
+        <v>2235.19</v>
+      </c>
+      <c r="I229">
+        <v>4.754</v>
+      </c>
+      <c r="J229">
+        <v>6989.47</v>
+      </c>
+      <c r="K229">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L229">
+        <v>76530</v>
+      </c>
+      <c r="M229">
+        <v>44100</v>
+      </c>
+      <c r="N229">
+        <v>128</v>
+      </c>
+      <c r="O229">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>129</v>
+      </c>
+      <c r="C230" t="s">
+        <v>137</v>
+      </c>
+      <c r="D230" t="s">
+        <v>139</v>
+      </c>
+      <c r="E230" t="s">
+        <v>141</v>
+      </c>
+      <c r="F230">
+        <v>65</v>
+      </c>
+      <c r="G230">
+        <v>13</v>
+      </c>
+      <c r="H230">
+        <v>1899.78</v>
+      </c>
+      <c r="I230">
+        <v>3.669</v>
+      </c>
+      <c r="J230">
+        <v>5569.12</v>
+      </c>
+      <c r="K230">
+        <v>11.67</v>
+      </c>
+      <c r="L230">
+        <v>161862</v>
+      </c>
+      <c r="M230">
+        <v>22050</v>
+      </c>
+      <c r="N230">
+        <v>352.9</v>
+      </c>
+      <c r="O230">
+        <v>0.0975</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>130</v>
+      </c>
+      <c r="C231" t="s">
+        <v>136</v>
+      </c>
+      <c r="D231" t="s">
+        <v>138</v>
+      </c>
+      <c r="E231" t="s">
+        <v>140</v>
+      </c>
+      <c r="F231">
+        <v>42</v>
+      </c>
+      <c r="G231">
+        <v>10</v>
+      </c>
+      <c r="H231">
+        <v>1922.03</v>
+      </c>
+      <c r="I231">
+        <v>2.508</v>
+      </c>
+      <c r="J231">
+        <v>4429.79</v>
+      </c>
+      <c r="K231">
+        <v>9.48</v>
+      </c>
+      <c r="L231">
+        <v>40586</v>
+      </c>
+      <c r="M231">
+        <v>44100</v>
+      </c>
+      <c r="N231">
+        <v>128</v>
+      </c>
+      <c r="O231">
+        <v>0.168</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>130</v>
+      </c>
+      <c r="C232" t="s">
+        <v>137</v>
+      </c>
+      <c r="D232" t="s">
+        <v>139</v>
+      </c>
+      <c r="E232" t="s">
+        <v>141</v>
+      </c>
+      <c r="F232">
+        <v>42</v>
+      </c>
+      <c r="G232">
+        <v>10</v>
+      </c>
+      <c r="H232">
+        <v>2347.59</v>
+      </c>
+      <c r="I232">
+        <v>3.072</v>
+      </c>
+      <c r="J232">
+        <v>5419.61</v>
+      </c>
+      <c r="K232">
+        <v>7.75</v>
+      </c>
+      <c r="L232">
+        <v>135520</v>
+      </c>
+      <c r="M232">
+        <v>22050</v>
+      </c>
+      <c r="N232">
+        <v>352.91</v>
+      </c>
+      <c r="O232">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>131</v>
+      </c>
+      <c r="C233" t="s">
+        <v>136</v>
+      </c>
+      <c r="D233" t="s">
+        <v>138</v>
+      </c>
+      <c r="E233" t="s">
+        <v>140</v>
+      </c>
+      <c r="F233">
+        <v>34</v>
+      </c>
+      <c r="G233">
+        <v>8</v>
+      </c>
+      <c r="H233">
+        <v>1302.59</v>
+      </c>
+      <c r="I233">
+        <v>2.508</v>
+      </c>
+      <c r="J233">
+        <v>3810.35</v>
+      </c>
+      <c r="K233">
+        <v>8.92</v>
+      </c>
+      <c r="L233">
+        <v>40586</v>
+      </c>
+      <c r="M233">
+        <v>44100</v>
+      </c>
+      <c r="N233">
+        <v>128</v>
+      </c>
+      <c r="O233">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>131</v>
+      </c>
+      <c r="C234" t="s">
+        <v>137</v>
+      </c>
+      <c r="D234" t="s">
+        <v>139</v>
+      </c>
+      <c r="E234" t="s">
+        <v>141</v>
+      </c>
+      <c r="F234">
+        <v>34</v>
+      </c>
+      <c r="G234">
+        <v>8</v>
+      </c>
+      <c r="H234">
+        <v>1352.84</v>
+      </c>
+      <c r="I234">
+        <v>2.219</v>
+      </c>
+      <c r="J234">
+        <v>3571.53</v>
+      </c>
+      <c r="K234">
+        <v>9.52</v>
+      </c>
+      <c r="L234">
+        <v>97888</v>
+      </c>
+      <c r="M234">
+        <v>22050</v>
+      </c>
+      <c r="N234">
+        <v>352.96</v>
+      </c>
+      <c r="O234">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>132</v>
+      </c>
+      <c r="C235" t="s">
+        <v>136</v>
+      </c>
+      <c r="D235" t="s">
+        <v>138</v>
+      </c>
+      <c r="E235" t="s">
+        <v>140</v>
+      </c>
+      <c r="F235">
+        <v>25</v>
+      </c>
+      <c r="G235">
+        <v>6</v>
+      </c>
+      <c r="H235">
+        <v>1400.03</v>
+      </c>
+      <c r="I235">
+        <v>2.116</v>
+      </c>
+      <c r="J235">
+        <v>3515.95</v>
+      </c>
+      <c r="K235">
+        <v>7.11</v>
+      </c>
+      <c r="L235">
+        <v>34316</v>
+      </c>
+      <c r="M235">
+        <v>44100</v>
+      </c>
+      <c r="N235">
+        <v>128</v>
+      </c>
+      <c r="O235">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>132</v>
+      </c>
+      <c r="C236" t="s">
+        <v>137</v>
+      </c>
+      <c r="D236" t="s">
+        <v>139</v>
+      </c>
+      <c r="E236" t="s">
+        <v>141</v>
+      </c>
+      <c r="F236">
+        <v>25</v>
+      </c>
+      <c r="G236">
+        <v>6</v>
+      </c>
+      <c r="H236">
+        <v>1383.73</v>
+      </c>
+      <c r="I236">
+        <v>1.877</v>
+      </c>
+      <c r="J236">
+        <v>3261.06</v>
+      </c>
+      <c r="K236">
+        <v>7.67</v>
+      </c>
+      <c r="L236">
+        <v>82834</v>
+      </c>
+      <c r="M236">
+        <v>22050</v>
+      </c>
+      <c r="N236">
+        <v>352.99</v>
+      </c>
+      <c r="O236">
+        <v>0.0375</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>133</v>
+      </c>
+      <c r="C237" t="s">
+        <v>136</v>
+      </c>
+      <c r="D237" t="s">
+        <v>138</v>
+      </c>
+      <c r="E237" t="s">
+        <v>140</v>
+      </c>
+      <c r="F237">
+        <v>35</v>
+      </c>
+      <c r="G237">
+        <v>7</v>
+      </c>
+      <c r="H237">
+        <v>1648.56</v>
+      </c>
+      <c r="I237">
+        <v>2.586</v>
+      </c>
+      <c r="J237">
+        <v>4234.68</v>
+      </c>
+      <c r="K237">
+        <v>8.27</v>
+      </c>
+      <c r="L237">
+        <v>41839</v>
+      </c>
+      <c r="M237">
+        <v>44100</v>
+      </c>
+      <c r="N237">
+        <v>128</v>
+      </c>
+      <c r="O237">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>133</v>
+      </c>
+      <c r="C238" t="s">
+        <v>137</v>
+      </c>
+      <c r="D238" t="s">
+        <v>139</v>
+      </c>
+      <c r="E238" t="s">
+        <v>141</v>
+      </c>
+      <c r="F238">
+        <v>35</v>
+      </c>
+      <c r="G238">
+        <v>7</v>
+      </c>
+      <c r="H238">
+        <v>2098.7</v>
+      </c>
+      <c r="I238">
+        <v>3.755</v>
+      </c>
+      <c r="J238">
+        <v>5853.35</v>
+      </c>
+      <c r="K238">
+        <v>5.98</v>
+      </c>
+      <c r="L238">
+        <v>165624</v>
+      </c>
+      <c r="M238">
+        <v>22050</v>
+      </c>
+      <c r="N238">
+        <v>352.89</v>
+      </c>
+      <c r="O238">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>134</v>
+      </c>
+      <c r="C239" t="s">
+        <v>136</v>
+      </c>
+      <c r="D239" t="s">
+        <v>138</v>
+      </c>
+      <c r="E239" t="s">
+        <v>140</v>
+      </c>
+      <c r="F239">
+        <v>43</v>
+      </c>
+      <c r="G239">
+        <v>10</v>
+      </c>
+      <c r="H239">
+        <v>1868.68</v>
+      </c>
+      <c r="I239">
+        <v>3.866</v>
+      </c>
+      <c r="J239">
+        <v>5734.8</v>
+      </c>
+      <c r="K239">
+        <v>7.5</v>
+      </c>
+      <c r="L239">
+        <v>62319</v>
+      </c>
+      <c r="M239">
+        <v>44100</v>
+      </c>
+      <c r="N239">
+        <v>128</v>
+      </c>
+      <c r="O239">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>134</v>
+      </c>
+      <c r="C240" t="s">
+        <v>137</v>
+      </c>
+      <c r="D240" t="s">
+        <v>139</v>
+      </c>
+      <c r="E240" t="s">
+        <v>141</v>
+      </c>
+      <c r="F240">
+        <v>43</v>
+      </c>
+      <c r="G240">
+        <v>10</v>
+      </c>
+      <c r="H240">
+        <v>2282.94</v>
+      </c>
+      <c r="I240">
+        <v>3.84</v>
+      </c>
+      <c r="J240">
+        <v>6122.94</v>
+      </c>
+      <c r="K240">
+        <v>7.02</v>
+      </c>
+      <c r="L240">
+        <v>169388</v>
+      </c>
+      <c r="M240">
+        <v>22050</v>
+      </c>
+      <c r="N240">
+        <v>352.89</v>
+      </c>
+      <c r="O240">
+        <v>0.0645</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>135</v>
+      </c>
+      <c r="C241" t="s">
+        <v>136</v>
+      </c>
+      <c r="D241" t="s">
+        <v>138</v>
+      </c>
+      <c r="E241" t="s">
+        <v>140</v>
+      </c>
+      <c r="F241">
+        <v>35</v>
+      </c>
+      <c r="G241">
+        <v>7</v>
+      </c>
+      <c r="H241">
+        <v>1539.54</v>
+      </c>
+      <c r="I241">
+        <v>2.691</v>
+      </c>
+      <c r="J241">
+        <v>4230.15</v>
+      </c>
+      <c r="K241">
+        <v>8.27</v>
+      </c>
+      <c r="L241">
+        <v>43511</v>
+      </c>
+      <c r="M241">
+        <v>44100</v>
+      </c>
+      <c r="N241">
+        <v>128</v>
+      </c>
+      <c r="O241">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>135</v>
+      </c>
+      <c r="C242" t="s">
+        <v>137</v>
+      </c>
+      <c r="D242" t="s">
+        <v>139</v>
+      </c>
+      <c r="E242" t="s">
+        <v>141</v>
+      </c>
+      <c r="F242">
+        <v>35</v>
+      </c>
+      <c r="G242">
+        <v>7</v>
+      </c>
+      <c r="H242">
+        <v>1573.58</v>
+      </c>
+      <c r="I242">
+        <v>2.645</v>
+      </c>
+      <c r="J242">
+        <v>4218.94</v>
+      </c>
+      <c r="K242">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L242">
+        <v>116704</v>
+      </c>
+      <c r="M242">
+        <v>22050</v>
+      </c>
+      <c r="N242">
+        <v>352.93</v>
+      </c>
+      <c r="O242">
         <v>0.0525</v>
       </c>
     </row>
